--- a/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов ХВ.xlsx
+++ b/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[539.98, 556.64, 585.43]</t>
+          <t>[475.79, 739.34, 773.79]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[544.33, 634.45, 733.22]</t>
+          <t>[495.67, 679.44, 710.13]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>96.46495661845026</v>
+        <v>51.7554147139668</v>
       </c>
       <c r="G2" t="n">
-        <v>76.64995101286225</v>
+        <v>47.81291429607452</v>
       </c>
       <c r="H2" t="n">
-        <v>11.07312453926559</v>
+        <v>7.263683367103507</v>
       </c>
     </row>
     <row r="3">
@@ -514,32 +514,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[557.52, 586.08, 653.24]</t>
+          <t>[742.36, 777.1, 809.27]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[634.45, 733.22, 686.11]</t>
+          <t>[679.44, 710.13, 843.07]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>97.72077566469655</v>
+        <v>56.52678763232484</v>
       </c>
       <c r="G3" t="n">
-        <v>85.64549747367869</v>
+        <v>54.56265658445579</v>
       </c>
       <c r="H3" t="n">
-        <v>12.32782335261049</v>
+        <v>7.566669401044616</v>
       </c>
     </row>
     <row r="4">
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[596.32, 658.54, 769.98]</t>
+          <t>[770.29, 803.99, 648.14]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[733.22, 686.11, 756.58]</t>
+          <t>[710.13, 843.07, 717.2]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>80.99688255260212</v>
+        <v>57.49211495865783</v>
       </c>
       <c r="G4" t="n">
-        <v>59.29185121755942</v>
+        <v>56.10015807952004</v>
       </c>
       <c r="H4" t="n">
-        <v>8.153749195981202</v>
+        <v>7.578796576935683</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[666.09, 782.4, 777.1]</t>
+          <t>[800.21, 647.9, 556.45]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[686.11, 756.58, 825.36]</t>
+          <t>[843.07, 717.2, 606.56]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33.64476554921223</v>
+        <v>55.22591653253853</v>
       </c>
       <c r="G5" t="n">
-        <v>31.36396750528354</v>
+        <v>54.08780659024762</v>
       </c>
       <c r="H5" t="n">
-        <v>4.058913530123925</v>
+        <v>7.668889046698235</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +622,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[784.38, 779.21, 505.68]</t>
+          <t>[649.1, 557.46, 618.78]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[756.58, 825.36, 499.73]</t>
+          <t>[717.2, 606.56, 807.76]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>31.29509615382529</v>
+        <v>119.3887079422173</v>
       </c>
       <c r="G6" t="n">
-        <v>26.63335253766089</v>
+        <v>102.0596069764857</v>
       </c>
       <c r="H6" t="n">
-        <v>3.485475199025435</v>
+        <v>13.66186510741766</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[776.24, 504.38, 473.96]</t>
+          <t>[561.58, 620.97, 680.12]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[825.36, 499.73, 495.67]</t>
+          <t>[606.56, 807.76, 799.68]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31.12382973746631</v>
+        <v>130.6525683200885</v>
       </c>
       <c r="G7" t="n">
-        <v>25.16288580096129</v>
+        <v>117.1121465101233</v>
       </c>
       <c r="H7" t="n">
-        <v>3.754469427846535</v>
+        <v>15.16393469028339</v>
       </c>
     </row>
     <row r="8">
@@ -694,32 +694,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[506.75, 476.54, 740.61]</t>
+          <t>[623.24, 679.57, 681.42]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[499.73, 495.67, 679.44]</t>
+          <t>[807.76, 799.68, 798.4]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>37.22253352561614</v>
+        <v>143.9420603720211</v>
       </c>
       <c r="G8" t="n">
-        <v>29.10487109079689</v>
+        <v>140.5363490112393</v>
       </c>
       <c r="H8" t="n">
-        <v>4.755425206012228</v>
+        <v>17.50495432850299</v>
       </c>
     </row>
     <row r="9">
@@ -730,32 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[475.79, 739.34, 773.79]</t>
+          <t>[701.67, 698.64, 794.12]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[495.67, 679.44, 710.13]</t>
+          <t>[799.68, 798.4, 819.95]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>51.7554147139668</v>
+        <v>82.10785459049924</v>
       </c>
       <c r="G9" t="n">
-        <v>47.81291429607452</v>
+        <v>74.53221029054362</v>
       </c>
       <c r="H9" t="n">
-        <v>7.263683367103507</v>
+        <v>9.300308481174751</v>
       </c>
     </row>
     <row r="10">
@@ -766,32 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[742.36, 777.1, 809.27]</t>
+          <t>[710.94, 800.73, 848.3]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[679.44, 710.13, 843.07]</t>
+          <t>[798.4, 819.95, 909.79]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>56.52678763232484</v>
+        <v>62.7141241015122</v>
       </c>
       <c r="G10" t="n">
-        <v>54.56265658445579</v>
+        <v>56.05481870669413</v>
       </c>
       <c r="H10" t="n">
-        <v>7.566669401044616</v>
+        <v>6.685506418050253</v>
       </c>
     </row>
     <row r="11">
@@ -802,32 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[770.29, 803.99, 648.14]</t>
+          <t>[900.79, 946.83, 581.04]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[710.13, 843.07, 717.2]</t>
+          <t>[819.95, 909.79, 525.54]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>57.49211495865783</v>
+        <v>60.51942027614332</v>
       </c>
       <c r="G11" t="n">
-        <v>56.10015807952004</v>
+        <v>57.79498929373475</v>
       </c>
       <c r="H11" t="n">
-        <v>7.578796576935683</v>
+        <v>8.163789693821617</v>
       </c>
     </row>
     <row r="12">
@@ -838,32 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[1065.59, 479.5, 2412.12]</t>
+          <t>[1542.0, 1998.95, 1739.72]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[1205.91, 531.99, 2729.71]</t>
+          <t>[1502.85, 1973.46, 1734.09]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>202.73774089525</v>
+        <v>27.16691635016145</v>
       </c>
       <c r="G12" t="n">
-        <v>170.1318986254738</v>
+        <v>23.42282127835066</v>
       </c>
       <c r="H12" t="n">
-        <v>11.04549417660122</v>
+        <v>1.407107506894138</v>
       </c>
     </row>
     <row r="13">
@@ -874,32 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[506.62, 2544.71, 1639.82]</t>
+          <t>[1976.04, 1719.73, 2561.98]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[531.99, 2729.71, 1795.23]</t>
+          <t>[1973.46, 1734.09, 2559.49]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>140.2621751084494</v>
+        <v>8.544208109593267</v>
       </c>
       <c r="G13" t="n">
-        <v>121.9257155991524</v>
+        <v>6.477197145912214</v>
       </c>
       <c r="H13" t="n">
-        <v>6.734204444940302</v>
+        <v>0.3520489217849281</v>
       </c>
     </row>
     <row r="14">
@@ -910,32 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[2599.12, 1669.77, 1043.32]</t>
+          <t>[1718.72, 2560.49, 4071.05]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[2729.71, 1795.23, 1230.68]</t>
+          <t>[1734.09, 2559.49, 3691.59]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>150.4402965532677</v>
+        <v>219.2633502110777</v>
       </c>
       <c r="G14" t="n">
-        <v>147.8026228976989</v>
+        <v>131.9444959233698</v>
       </c>
       <c r="H14" t="n">
-        <v>8.998819148644161</v>
+        <v>3.734845461537053</v>
       </c>
     </row>
     <row r="15">
@@ -946,32 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[1705.95, 1064.93, 1872.31]</t>
+          <t>[2570.78, 4086.83, 1245.34]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[1795.23, 1230.68, 1915.07]</t>
+          <t>[2559.49, 3691.59, 1267.28]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>111.4638963030963</v>
+        <v>228.635612066317</v>
       </c>
       <c r="G15" t="n">
-        <v>99.26451954991974</v>
+        <v>142.820831123081</v>
       </c>
       <c r="H15" t="n">
-        <v>6.891437154160405</v>
+        <v>4.292834192776126</v>
       </c>
     </row>
     <row r="16">
@@ -982,32 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[1096.2, 1915.56, 1234.76]</t>
+          <t>[4078.73, 1242.94, 541.69]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[1230.68, 1915.07, 1199.71]</t>
+          <t>[3691.59, 1267.28, 536.79]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>80.23386600360756</v>
+        <v>223.974697344776</v>
       </c>
       <c r="G16" t="n">
-        <v>56.67214101582681</v>
+        <v>138.7921066087338</v>
       </c>
       <c r="H16" t="n">
-        <v>4.624665061215595</v>
+        <v>4.439966766571534</v>
       </c>
     </row>
     <row r="17">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[2009.37, 1304.17, 1619.57]</t>
+          <t>[1190.19, 517.58, 2602.49]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[1915.07, 1199.71, 1502.85]</t>
+          <t>[1267.28, 536.79, 2929.62]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>105.560581231177</v>
+        <v>194.3562040350583</v>
       </c>
       <c r="G17" t="n">
-        <v>105.1617291577647</v>
+        <v>141.1406277312812</v>
       </c>
       <c r="H17" t="n">
-        <v>7.13270691318884</v>
+        <v>6.94240433608261</v>
       </c>
     </row>
     <row r="18">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[1276.74, 1586.05, 2053.52]</t>
+          <t>[532.32, 2676.2, 1735.45]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[1199.71, 1502.85, 1973.46]</t>
+          <t>[536.79, 2929.62, 1795.06]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>80.13590125139397</v>
+        <v>150.3250109629953</v>
       </c>
       <c r="G18" t="n">
-        <v>80.09618408153499</v>
+        <v>105.8325411611595</v>
       </c>
       <c r="H18" t="n">
-        <v>5.337858536583364</v>
+        <v>4.267923846938138</v>
       </c>
     </row>
     <row r="19">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[1542.0, 1998.95, 1739.72]</t>
+          <t>[2686.27, 1741.95, 1139.84]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[1502.85, 1973.46, 1734.09]</t>
+          <t>[2929.62, 1795.06, 1235.48]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>27.16691635016145</v>
+        <v>154.0392197956862</v>
       </c>
       <c r="G19" t="n">
-        <v>23.42282127835066</v>
+        <v>130.6964979750079</v>
       </c>
       <c r="H19" t="n">
-        <v>1.407107506894138</v>
+        <v>6.335254381202167</v>
       </c>
     </row>
     <row r="20">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[1976.04, 1719.73, 2561.98]</t>
+          <t>[1812.0, 1184.72, 1904.04]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[1973.46, 1734.09, 2559.49]</t>
+          <t>[1795.06, 1235.48, 2052.14]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8.544208109593267</v>
+        <v>90.91331808732248</v>
       </c>
       <c r="G20" t="n">
-        <v>6.477197145912214</v>
+        <v>71.93102318009915</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3520489217849281</v>
+        <v>4.089551471386698</v>
       </c>
     </row>
     <row r="21">
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[1718.72, 2560.49, 4071.05]</t>
+          <t>[1179.48, 1896.11, 1224.22]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[1734.09, 2559.49, 3691.59]</t>
+          <t>[1235.48, 2052.14, 1244.06]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>219.2633502110777</v>
+        <v>96.39122390466559</v>
       </c>
       <c r="G21" t="n">
-        <v>131.9444959233698</v>
+        <v>77.28845247801739</v>
       </c>
       <c r="H21" t="n">
-        <v>3.734845461537053</v>
+        <v>4.576803552776663</v>
       </c>
     </row>
     <row r="22">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[937.63, 557.95, 3310.36]</t>
+          <t>[2490.04, 3374.83, 1767.94]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[1063.19, 470.8, 3663.52]</t>
+          <t>[2521.78, 4370.94, 1327.73]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>222.1741197032609</v>
+        <v>629.0290613668915</v>
       </c>
       <c r="G22" t="n">
-        <v>188.6248462899791</v>
+        <v>489.3563954971684</v>
       </c>
       <c r="H22" t="n">
-        <v>13.32048418186068</v>
+        <v>19.06786194333239</v>
       </c>
     </row>
     <row r="23">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[594.78, 3534.14, 821.87]</t>
+          <t>[3396.72, 1779.91, 3158.95]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[470.8, 3663.52, 779.14]</t>
+          <t>[4370.94, 1327.73, 2912.92]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>106.3575443150189</v>
+        <v>636.1616959245076</v>
       </c>
       <c r="G23" t="n">
-        <v>98.69673676289439</v>
+        <v>557.4776155003036</v>
       </c>
       <c r="H23" t="n">
-        <v>11.78351167951754</v>
+        <v>21.59715768333199</v>
       </c>
     </row>
     <row r="24">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[3141.42, 728.38, 928.37]</t>
+          <t>[2024.74, 3593.96, 9286.73]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[3663.52, 779.14, 1021.16]</t>
+          <t>[1327.73, 2912.92, 8213.9]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>307.5571083053174</v>
+        <v>836.7763726745966</v>
       </c>
       <c r="G24" t="n">
-        <v>221.8829476946337</v>
+        <v>816.9563814736517</v>
       </c>
       <c r="H24" t="n">
-        <v>9.95096334823209</v>
+        <v>29.64569670433833</v>
       </c>
     </row>
     <row r="25">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[785.02, 1003.74, 2780.01]</t>
+          <t>[2924.23, 7679.92, 1089.74]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[779.14, 1021.16, 3147.81]</t>
+          <t>[2912.92, 8213.9, 1113.56]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>212.6128064422834</v>
+        <v>308.669464065737</v>
       </c>
       <c r="G25" t="n">
-        <v>130.3675838750097</v>
+        <v>189.7025320045369</v>
       </c>
       <c r="H25" t="n">
-        <v>4.715167910720699</v>
+        <v>3.009355783252956</v>
       </c>
     </row>
     <row r="26">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[1000.1, 2769.66, 808.42]</t>
+          <t>[7666.42, 1087.81, 533.98]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[1021.16, 3147.81, 939.73]</t>
+          <t>[8213.9, 1113.56, 526.89]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>231.4334471732302</v>
+        <v>316.4644206251516</v>
       </c>
       <c r="G26" t="n">
-        <v>176.8400090829378</v>
+        <v>193.4391526953273</v>
       </c>
       <c r="H26" t="n">
-        <v>9.349490437719858</v>
+        <v>3.440849303192695</v>
       </c>
     </row>
     <row r="27">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[2797.75, 816.29, 2240.28]</t>
+          <t>[1124.42, 551.38, 4038.73]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[3147.81, 939.73, 2521.78]</t>
+          <t>[1113.56, 526.89, 3722.4]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>268.9646584586392</v>
+        <v>183.2897077118354</v>
       </c>
       <c r="G27" t="n">
-        <v>251.6694305297134</v>
+        <v>117.2294979605518</v>
       </c>
       <c r="H27" t="n">
-        <v>11.80654671411749</v>
+        <v>4.707324354310988</v>
       </c>
     </row>
     <row r="28">
@@ -1414,32 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[868.34, 2382.38, 3237.01]</t>
+          <t>[548.99, 4020.02, 855.63]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[939.73, 2521.78, 4370.94]</t>
+          <t>[526.89, 3722.4, 775.33]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>660.8892358274384</v>
+        <v>178.4308097057285</v>
       </c>
       <c r="G28" t="n">
-        <v>448.2386215872939</v>
+        <v>133.3390338781866</v>
       </c>
       <c r="H28" t="n">
-        <v>13.02236175380027</v>
+        <v>7.515500337284091</v>
       </c>
     </row>
     <row r="29">
@@ -1450,32 +1450,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[2490.04, 3374.83, 1767.94]</t>
+          <t>[3946.72, 840.02, 1094.49]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[2521.78, 4370.94, 1327.73]</t>
+          <t>[3722.4, 775.33, 937.06]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>629.0290613668915</v>
+        <v>162.5712777321382</v>
       </c>
       <c r="G29" t="n">
-        <v>489.3563954971684</v>
+        <v>148.8131428751515</v>
       </c>
       <c r="H29" t="n">
-        <v>19.06786194333239</v>
+        <v>10.39009882547584</v>
       </c>
     </row>
     <row r="30">
@@ -1486,32 +1486,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[3396.72, 1779.91, 3158.95]</t>
+          <t>[817.41, 1064.46, 3106.87]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[4370.94, 1327.73, 2912.92]</t>
+          <t>[775.33, 937.06, 3243.32]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>636.1616959245076</v>
+        <v>110.4842718165531</v>
       </c>
       <c r="G30" t="n">
-        <v>557.4776155003036</v>
+        <v>101.975933544014</v>
       </c>
       <c r="H30" t="n">
-        <v>21.59715768333199</v>
+        <v>7.743289934575051</v>
       </c>
     </row>
     <row r="31">
@@ -1522,32 +1522,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[2024.74, 3593.96, 9286.73]</t>
+          <t>[1038.59, 3030.53, 863.13]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[1327.73, 2912.92, 8213.9]</t>
+          <t>[937.06, 3243.32, 950.93]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>836.7763726745966</v>
+        <v>145.2517208685573</v>
       </c>
       <c r="G31" t="n">
-        <v>816.9563814736517</v>
+        <v>134.0366400114577</v>
       </c>
       <c r="H31" t="n">
-        <v>29.64569670433833</v>
+        <v>8.876010182071441</v>
       </c>
     </row>
     <row r="32">
@@ -1558,32 +1558,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[517.92, 567.29, 1015.91]</t>
+          <t>[1001.12, 912.06, 882.01]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[481.67, 585.47, 1013.82]</t>
+          <t>[921.73, 1014.74, 936.86]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>23.44551167883288</v>
+        <v>81.35447771501291</v>
       </c>
       <c r="G32" t="n">
-        <v>18.84144935543877</v>
+        <v>78.97564300231552</v>
       </c>
       <c r="H32" t="n">
-        <v>3.612639501951277</v>
+        <v>8.195795590441364</v>
       </c>
     </row>
     <row r="33">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[560.22, 1004.02, 789.13]</t>
+          <t>[905.6, 874.27, 945.72]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[585.47, 1013.82, 770.96]</t>
+          <t>[1014.74, 936.86, 713.69]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>18.82991103627469</v>
+        <v>152.3915238169082</v>
       </c>
       <c r="G33" t="n">
-        <v>17.74038794763957</v>
+        <v>134.5890450717305</v>
       </c>
       <c r="H33" t="n">
-        <v>2.545381301570506</v>
+        <v>16.64950310650042</v>
       </c>
     </row>
     <row r="34">
@@ -1630,32 +1630,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[1010.93, 793.75, 758.44]</t>
+          <t>[885.02, 952.61, 1899.11]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[1013.82, 770.96, 715.65]</t>
+          <t>[936.86, 713.69, 1886.37]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>28.03982148985698</v>
+        <v>141.3395502444723</v>
       </c>
       <c r="G34" t="n">
-        <v>22.82321196142531</v>
+        <v>101.1656948470018</v>
       </c>
       <c r="H34" t="n">
-        <v>3.073404031711743</v>
+        <v>13.22838470354839</v>
       </c>
     </row>
     <row r="35">
@@ -1666,32 +1666,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[794.0, 758.71, 2621.54]</t>
+          <t>[958.45, 1910.67, 496.8]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[770.96, 715.65, 2671.34]</t>
+          <t>[713.69, 1886.37, 488.55]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>40.27061489246063</v>
+        <v>142.0878650244802</v>
       </c>
       <c r="G35" t="n">
-        <v>38.63435989506846</v>
+        <v>92.43718796330982</v>
       </c>
       <c r="H35" t="n">
-        <v>3.623260830418678</v>
+        <v>12.42417970121229</v>
       </c>
     </row>
     <row r="36">
@@ -1702,32 +1702,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[756.19, 2613.08, 738.22]</t>
+          <t>[1835.22, 484.78, 560.38]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[715.65, 2671.34, 734.44]</t>
+          <t>[1886.37, 488.55, 574.6]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>41.03298362961279</v>
+        <v>30.73006292123565</v>
       </c>
       <c r="G36" t="n">
-        <v>34.1910541670704</v>
+        <v>23.0483665470161</v>
       </c>
       <c r="H36" t="n">
-        <v>2.786635811207065</v>
+        <v>1.986223421919944</v>
       </c>
     </row>
     <row r="37">
@@ -1738,32 +1738,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[2596.1, 733.52, 998.22]</t>
+          <t>[486.17, 562.37, 989.81]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[2671.34, 734.44, 921.73]</t>
+          <t>[488.55, 574.6, 986.83]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>61.95083404906364</v>
+        <v>7.397877432031752</v>
       </c>
       <c r="G37" t="n">
-        <v>50.88631811155142</v>
+        <v>5.86333016299767</v>
       </c>
       <c r="H37" t="n">
-        <v>3.747042118355016</v>
+        <v>0.9726134465663194</v>
       </c>
     </row>
     <row r="38">
@@ -1774,32 +1774,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[736.01, 1001.35, 912.3]</t>
+          <t>[562.69, 990.4, 760.46]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[734.44, 921.73, 1014.74]</t>
+          <t>[574.6, 986.83, 812.85]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>74.9137158350229</v>
+        <v>31.08503277742945</v>
       </c>
       <c r="G38" t="n">
-        <v>61.20977149336462</v>
+        <v>22.62137553826441</v>
       </c>
       <c r="H38" t="n">
-        <v>6.315631167967039</v>
+        <v>2.959679151210924</v>
       </c>
     </row>
     <row r="39">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[1001.12, 912.06, 882.01]</t>
+          <t>[992.75, 762.28, 721.6]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[921.73, 1014.74, 936.86]</t>
+          <t>[986.83, 812.85, 755.93]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>81.35447771501291</v>
+        <v>35.45370675115428</v>
       </c>
       <c r="G39" t="n">
-        <v>78.97564300231552</v>
+        <v>30.2723665801736</v>
       </c>
       <c r="H39" t="n">
-        <v>8.195795590441364</v>
+        <v>3.787438616952122</v>
       </c>
     </row>
     <row r="40">
@@ -1846,32 +1846,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[905.6, 874.27, 945.72]</t>
+          <t>[761.78, 721.12, 2597.04]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[1014.74, 936.86, 713.69]</t>
+          <t>[812.85, 755.93, 2961.75]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>152.3915238169082</v>
+        <v>213.56650846576</v>
       </c>
       <c r="G40" t="n">
-        <v>134.5890450717305</v>
+        <v>150.1960042472996</v>
       </c>
       <c r="H40" t="n">
-        <v>16.64950310650042</v>
+        <v>7.733884286800407</v>
       </c>
     </row>
     <row r="41">
@@ -1882,32 +1882,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[885.02, 952.61, 1899.11]</t>
+          <t>[726.04, 2615.03, 729.08]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[936.86, 713.69, 1886.37]</t>
+          <t>[755.93, 2961.75, 744.45]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>141.3395502444723</v>
+        <v>201.117053659995</v>
       </c>
       <c r="G41" t="n">
-        <v>101.1656948470018</v>
+        <v>130.659833684147</v>
       </c>
       <c r="H41" t="n">
-        <v>13.22838470354839</v>
+        <v>5.908412839667545</v>
       </c>
     </row>
     <row r="42">
@@ -1918,32 +1918,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[422.89, 655.96, 921.95]</t>
+          <t>[700.16, 1879.83, 1002.3]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[463.04, 727.88, 1115.63]</t>
+          <t>[749.4, 1738.77, 941.21]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>121.5131961405034</v>
+        <v>93.19093511828719</v>
       </c>
       <c r="G42" t="n">
-        <v>101.9187635693253</v>
+        <v>83.79560133816051</v>
       </c>
       <c r="H42" t="n">
-        <v>11.97121560006281</v>
+        <v>7.057859714335677</v>
       </c>
     </row>
     <row r="43">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[689.05, 971.78, 815.09]</t>
+          <t>[1946.13, 1035.09, 1463.79]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[727.88, 1115.63, 856.29]</t>
+          <t>[1738.77, 941.21, 1485.16]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>89.25406098654557</v>
+        <v>131.997643918047</v>
       </c>
       <c r="G43" t="n">
-        <v>74.62658221457154</v>
+        <v>107.5398113579945</v>
       </c>
       <c r="H43" t="n">
-        <v>7.680003872006484</v>
+        <v>7.779876178553034</v>
       </c>
     </row>
     <row r="44">
@@ -1990,32 +1990,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[1001.02, 839.11, 936.7]</t>
+          <t>[976.75, 1381.27, 3778.17]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[1115.63, 856.29, 898.75]</t>
+          <t>[941.21, 1485.16, 3244.57]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>70.40627859334217</v>
+        <v>314.5306409779039</v>
       </c>
       <c r="G44" t="n">
-        <v>56.58077966279856</v>
+        <v>224.3453967532755</v>
       </c>
       <c r="H44" t="n">
-        <v>5.500739470562247</v>
+        <v>9.07253620722858</v>
       </c>
     </row>
     <row r="45">
@@ -2026,32 +2026,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[886.23, 989.56, 1346.49]</t>
+          <t>[1354.76, 3708.42, 510.87]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[856.29, 898.75, 1520.02]</t>
+          <t>[1485.16, 3244.57, 516.73]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>114.3930714552611</v>
+        <v>278.208183333576</v>
       </c>
       <c r="G45" t="n">
-        <v>98.0946042515955</v>
+        <v>200.0375950197806</v>
       </c>
       <c r="H45" t="n">
-        <v>8.33900232595024</v>
+        <v>8.069979263715474</v>
       </c>
     </row>
     <row r="46">
@@ -2062,32 +2062,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[972.9, 1323.83, 1254.88]</t>
+          <t>[3885.3, 535.68, 817.64]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[898.75, 1520.02, 1404.39]</t>
+          <t>[3244.57, 516.73, 716.8]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>148.70843943483</v>
+        <v>374.6369918017206</v>
       </c>
       <c r="G46" t="n">
-        <v>139.9506750302039</v>
+        <v>253.5059655968261</v>
       </c>
       <c r="H46" t="n">
-        <v>10.60115411402903</v>
+        <v>12.4943689919435</v>
       </c>
     </row>
     <row r="47">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[1273.13, 1207.01, 615.82]</t>
+          <t>[489.69, 749.26, 1087.62]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[1520.02, 1404.39, 749.4]</t>
+          <t>[516.73, 716.8, 1048.98]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>198.120878205592</v>
+        <v>33.05264611122759</v>
       </c>
       <c r="G47" t="n">
-        <v>192.6155784051154</v>
+        <v>32.71129726811336</v>
       </c>
       <c r="H47" t="n">
-        <v>16.04060134932145</v>
+        <v>4.481409110021231</v>
       </c>
     </row>
     <row r="48">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[1319.6, 675.21, 1817.37]</t>
+          <t>[770.3, 1119.13, 873.94]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[1404.39, 749.4, 1738.77]</t>
+          <t>[716.8, 1048.98, 832.48]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>79.3128006238874</v>
+        <v>56.27985207700902</v>
       </c>
       <c r="G48" t="n">
-        <v>79.19363757151105</v>
+        <v>55.03736645200104</v>
       </c>
       <c r="H48" t="n">
-        <v>6.819350157444513</v>
+        <v>6.37724862491896</v>
       </c>
     </row>
     <row r="49">
@@ -2170,32 +2170,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[700.16, 1879.83, 1002.3]</t>
+          <t>[1077.25, 841.34, 918.94]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[749.4, 1738.77, 941.21]</t>
+          <t>[1048.98, 832.48, 946.63]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>93.19093511828719</v>
+        <v>23.4147452228148</v>
       </c>
       <c r="G49" t="n">
-        <v>83.79560133816051</v>
+        <v>21.60935147290688</v>
       </c>
       <c r="H49" t="n">
-        <v>7.057859714335677</v>
+        <v>2.2284196341916</v>
       </c>
     </row>
     <row r="50">
@@ -2206,32 +2206,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[1946.13, 1035.09, 1463.79]</t>
+          <t>[829.56, 906.2, 1403.17]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[1738.77, 941.21, 1485.16]</t>
+          <t>[832.48, 946.63, 1415.91]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>131.997643918047</v>
+        <v>24.53331502994952</v>
       </c>
       <c r="G50" t="n">
-        <v>107.5398113579945</v>
+        <v>18.69894968526144</v>
       </c>
       <c r="H50" t="n">
-        <v>7.779876178553034</v>
+        <v>1.840720596938869</v>
       </c>
     </row>
     <row r="51">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[976.75, 1381.27, 3778.17]</t>
+          <t>[907.82, 1405.7, 1261.3]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[941.21, 1485.16, 3244.57]</t>
+          <t>[946.63, 1415.91, 1527.06]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>314.5306409779039</v>
+        <v>155.1778918581501</v>
       </c>
       <c r="G51" t="n">
-        <v>224.3453967532755</v>
+        <v>104.9265393934487</v>
       </c>
       <c r="H51" t="n">
-        <v>9.07253620722858</v>
+        <v>7.408030704923449</v>
       </c>
     </row>
     <row r="52">
@@ -2278,29 +2278,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[0.12, 0.06, 0.42]</t>
+          <t>[-0.07, 0.23, 0.6]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[0.0, 0.0, 1.5]</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.3179118656602992</v>
+        <v>0.5355111041407038</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2912641586013051</v>
+        <v>0.3996129779699791</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2316,29 +2316,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[0.05, 0.41, 0.54]</t>
+          <t>[0.24, 0.61, 0.71]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.4]</t>
+          <t>[0.0, 1.5, 0.0]</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.3196446761720755</v>
+        <v>0.6682014268723393</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2994310458595659</v>
+        <v>0.6100680238357424</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2354,29 +2354,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[0.44, 0.58, 0.68]</t>
+          <t>[0.59, 0.68, 0.6]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.1]</t>
+          <t>[1.5, 0.0, 0.9]</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.4325411084229213</v>
+        <v>0.6781380666981623</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3998012270770335</v>
+        <v>0.6286076871288145</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2392,32 +2392,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[0.54, 0.63, 0.07]</t>
+          <t>[0.74, 0.66, 0.12]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[0.4, 0.1, 0.3]</t>
+          <t>[0.0, 0.9, 0.6]</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.3434416212985296</v>
+        <v>0.5261184226367263</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2989490873674395</v>
-      </c>
-      <c r="H55" t="n">
-        <v>214.0536947780057</v>
+        <v>0.4846993068462794</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -2428,29 +2430,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[0.62, 0.06, -0.25]</t>
+          <t>[0.59, 0.07, 0.06]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[0.1, 0.3, 0.0]</t>
+          <t>[0.9, 0.6, 0.0]</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.3597267745411392</v>
+        <v>0.3535043327453559</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3353608973272098</v>
+        <v>0.298569300926026</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2466,29 +2468,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[0.03, -0.27, -0.11]</t>
+          <t>[0.09, 0.08, 0.35]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[0.3, 0.0, 0.0]</t>
+          <t>[0.6, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.2309846173337714</v>
+        <v>0.3605021994628063</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2182433469659844</v>
+        <v>0.312923763518965</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2504,17 +2506,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[-0.26, -0.09, 0.2]</t>
+          <t>[0.11, 0.39, 0.57]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2523,10 +2525,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.1971906352822189</v>
+        <v>0.4037171222871691</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1850209902687118</v>
+        <v>0.3570669544554407</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2542,29 +2544,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[-0.07, 0.23, 0.6]</t>
+          <t>[0.38, 0.55, 0.6]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.5]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.5355111041407038</v>
+        <v>0.5217984029873278</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3996129779699791</v>
+        <v>0.5130693478241035</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2580,29 +2582,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[0.24, 0.61, 0.71]</t>
+          <t>[0.52, 0.56, 0.09]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[0.0, 1.5, 0.0]</t>
+          <t>[0.0, 0.0, 5.0]</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.6682014268723393</v>
+        <v>2.870265579657916</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6100680238357424</v>
+        <v>1.997030785225775</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2618,29 +2620,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[0.59, 0.68, 0.6]</t>
+          <t>[0.51, 0.05, -0.25]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[1.5, 0.0, 0.9]</t>
+          <t>[0.0, 5.0, 6.0]</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.6781380666981623</v>
+        <v>4.611653957797276</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6286076871288145</v>
+        <v>3.903152662981176</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2656,32 +2658,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0.78, 0.6, 0.99]</t>
+          <t>[2.44, 0.94, 1.06]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[0.7, 0.6, 1.3]</t>
+          <t>[2.0, 0.8, 0.8]</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.1843090328110902</v>
+        <v>0.3063981641053316</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1289925102927366</v>
+        <v>0.2812702892149177</v>
       </c>
       <c r="H62" t="n">
-        <v>11.61993841744241</v>
+        <v>24.17505087002144</v>
       </c>
     </row>
     <row r="63">
@@ -2692,32 +2694,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0.57, 0.95, 0.48]</t>
+          <t>[0.84, 0.94, 0.59]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[0.6, 1.3, 0.7]</t>
+          <t>[0.8, 0.8, 0.6]</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.2380717302217143</v>
+        <v>0.08609974617714722</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1991341098770822</v>
+        <v>0.06355165816671338</v>
       </c>
       <c r="H63" t="n">
-        <v>21.03606851624333</v>
+        <v>8.084933724303838</v>
       </c>
     </row>
     <row r="64">
@@ -2728,32 +2730,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[0.97, 0.49, 0.71]</t>
+          <t>[0.93, 0.58, 1.14]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[1.3, 0.7, 0.9]</t>
+          <t>[0.8, 0.6, 1.0]</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.2517854367882414</v>
+        <v>0.1126979580950248</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2439874824087544</v>
+        <v>0.09895316902993045</v>
       </c>
       <c r="H64" t="n">
-        <v>25.51287745369699</v>
+        <v>11.48448449110345</v>
       </c>
     </row>
     <row r="65">
@@ -2764,32 +2766,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0.6, 0.82, 0.78]</t>
+          <t>[0.53, 1.09, 0.64]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[0.7, 0.9, 0.7]</t>
+          <t>[0.6, 1.0, 0.7]</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.08713758696180389</v>
+        <v>0.07179427867177614</v>
       </c>
       <c r="G65" t="n">
-        <v>0.08628532035995513</v>
+        <v>0.07093014626615442</v>
       </c>
       <c r="H65" t="n">
-        <v>11.49498004598862</v>
+        <v>9.450730808611189</v>
       </c>
     </row>
     <row r="66">
@@ -2800,32 +2802,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0.87, 0.82, 1.22]</t>
+          <t>[1.12, 0.67, 0.56]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[0.9, 0.7, 1.1]</t>
+          <t>[1.0, 0.7, 0.7]</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.1033241852377227</v>
+        <v>0.1085731627147664</v>
       </c>
       <c r="G66" t="n">
-        <v>0.09300265787556261</v>
+        <v>0.09706523607348427</v>
       </c>
       <c r="H66" t="n">
-        <v>10.81502759095114</v>
+        <v>12.09053152083433</v>
       </c>
     </row>
     <row r="67">
@@ -2836,32 +2838,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0.84, 1.24, 2.6]</t>
+          <t>[0.63, 0.52, 1.05]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>[0.7, 1.1, 2.0]</t>
+          <t>[0.7, 0.7, 1.2]</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.3659341253255048</v>
+        <v>0.1382897192174451</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2932969603438276</v>
+        <v>0.1308399875027375</v>
       </c>
       <c r="H67" t="n">
-        <v>20.81963757205719</v>
+        <v>15.7883803262752</v>
       </c>
     </row>
     <row r="68">
@@ -2872,32 +2874,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[1.17, 2.48, 0.97]</t>
+          <t>[0.55, 1.09, 0.51]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[1.1, 2.0, 0.8]</t>
+          <t>[0.7, 1.2, 0.8]</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.2990283062116705</v>
+        <v>0.2006590257147154</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2402746283694243</v>
+        <v>0.1843276405518656</v>
       </c>
       <c r="H68" t="n">
-        <v>17.16224591240081</v>
+        <v>22.40558682780973</v>
       </c>
     </row>
     <row r="69">
@@ -2908,32 +2910,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[2.44, 0.94, 1.06]</t>
+          <t>[1.17, 0.57, 0.74]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[2.0, 0.8, 0.8]</t>
+          <t>[1.2, 0.8, 0.9]</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.3063981641053316</v>
+        <v>0.1653463689324808</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2812702892149177</v>
+        <v>0.1409697297480837</v>
       </c>
       <c r="H69" t="n">
-        <v>24.17505087002144</v>
+        <v>16.50738635588676</v>
       </c>
     </row>
     <row r="70">
@@ -2944,32 +2946,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0.84, 0.94, 0.59]</t>
+          <t>[0.57, 0.75, 0.61]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[0.8, 0.8, 0.6]</t>
+          <t>[0.8, 0.9, 0.7]</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.08609974617714722</v>
+        <v>0.1659127856718748</v>
       </c>
       <c r="G70" t="n">
-        <v>0.06355165816671338</v>
+        <v>0.1558243322495027</v>
       </c>
       <c r="H70" t="n">
-        <v>8.084933724303838</v>
+        <v>19.28421286386187</v>
       </c>
     </row>
     <row r="71">
@@ -2980,32 +2982,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0.93, 0.58, 1.14]</t>
+          <t>[0.85, 0.71, 1.13]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[0.8, 0.6, 1.0]</t>
+          <t>[0.9, 0.7, 1.1]</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.1126979580950248</v>
+        <v>0.03580382041969872</v>
       </c>
       <c r="G71" t="n">
-        <v>0.09895316902993045</v>
+        <v>0.03010577402366998</v>
       </c>
       <c r="H71" t="n">
-        <v>11.48448449110345</v>
+        <v>3.187590929538138</v>
       </c>
     </row>
     <row r="72">
@@ -3016,32 +3018,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[90.73, 65.23, 58.04]</t>
+          <t>[56.69, 58.65, 63.25]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[118.5, 78.6, 61.3]</t>
+          <t>[43.3, 53.6, 51.9]</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>17.89142740466846</v>
+        <v>10.54754523172072</v>
       </c>
       <c r="G72" t="n">
-        <v>14.79710390092095</v>
+        <v>9.932699019304335</v>
       </c>
       <c r="H72" t="n">
-        <v>15.25061201110723</v>
+        <v>20.7433144733832</v>
       </c>
     </row>
     <row r="73">
@@ -3052,32 +3054,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[69.16, 61.49, 53.58]</t>
+          <t>[56.06, 60.5, 58.93]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[78.6, 61.3, 49.0]</t>
+          <t>[53.6, 51.9, 80.83]</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6.060818840457769</v>
+        <v>13.65919823771045</v>
       </c>
       <c r="G73" t="n">
-        <v>4.738747436501377</v>
+        <v>10.9866355731143</v>
       </c>
       <c r="H73" t="n">
-        <v>7.22488011972982</v>
+        <v>16.08393491978726</v>
       </c>
     </row>
     <row r="74">
@@ -3088,32 +3090,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[63.22, 55.06, 56.83]</t>
+          <t>[60.06, 58.5, 193.85]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[61.3, 49.0, 48.5]</t>
+          <t>[51.9, 80.83, 212.13]</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6.050208309359251</v>
+        <v>17.31637675808157</v>
       </c>
       <c r="G74" t="n">
-        <v>5.437366639609519</v>
+        <v>16.25809918413555</v>
       </c>
       <c r="H74" t="n">
-        <v>10.89297245900119</v>
+        <v>17.32225705878599</v>
       </c>
     </row>
     <row r="75">
@@ -3124,32 +3126,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[54.69, 56.45, 69.84]</t>
+          <t>[57.11, 189.38, 100.76]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[49.0, 48.5, 216.12]</t>
+          <t>[80.83, 212.13, 108.39]</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>84.64381696340382</v>
+        <v>19.47941460136884</v>
       </c>
       <c r="G75" t="n">
-        <v>53.30856252481934</v>
+        <v>18.03326619021034</v>
       </c>
       <c r="H75" t="n">
-        <v>31.89962620217124</v>
+        <v>15.70250368914866</v>
       </c>
     </row>
     <row r="76">
@@ -3160,32 +3162,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[55.14, 68.26, 59.68]</t>
+          <t>[200.25, 106.5, 75.4]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[48.5, 216.12, 43.4]</t>
+          <t>[212.13, 108.39, 76.72]</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>85.96598183581305</v>
+        <v>6.987073408722422</v>
       </c>
       <c r="G76" t="n">
-        <v>56.92408673305493</v>
+        <v>5.030751281692285</v>
       </c>
       <c r="H76" t="n">
-        <v>39.86964023186685</v>
+        <v>3.022554333913813</v>
       </c>
     </row>
     <row r="77">
@@ -3196,32 +3198,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[66.44, 58.1, 50.13]</t>
+          <t>[107.5, 76.11, 66.1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>[216.12, 43.4, 43.3]</t>
+          <t>[108.39, 76.72, 63.56]</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>86.92566754610297</v>
+        <v>1.594385036288864</v>
       </c>
       <c r="G77" t="n">
-        <v>57.07348814979127</v>
+        <v>1.347739284305045</v>
       </c>
       <c r="H77" t="n">
-        <v>39.63960312652205</v>
+        <v>1.872655956952879</v>
       </c>
     </row>
     <row r="78">
@@ -3232,32 +3234,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[74.08, 63.72, 65.82]</t>
+          <t>[76.21, 66.19, 56.76]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[43.4, 43.3, 53.6]</t>
+          <t>[76.72, 63.56, 49.8]</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>22.41869541884958</v>
+        <v>4.303809789466457</v>
       </c>
       <c r="G78" t="n">
-        <v>21.10829154559359</v>
+        <v>3.365222193481017</v>
       </c>
       <c r="H78" t="n">
-        <v>46.88654791500235</v>
+        <v>6.256716726841151</v>
       </c>
     </row>
     <row r="79">
@@ -3268,32 +3270,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[56.69, 58.65, 63.25]</t>
+          <t>[66.27, 56.82, 58.16]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[43.3, 53.6, 51.9]</t>
+          <t>[63.56, 49.8, 48.0]</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>10.54754523172072</v>
+        <v>7.298866260313426</v>
       </c>
       <c r="G79" t="n">
-        <v>9.932699019304335</v>
+        <v>6.629732577883559</v>
       </c>
       <c r="H79" t="n">
-        <v>20.7433144733832</v>
+        <v>13.17475452235028</v>
       </c>
     </row>
     <row r="80">
@@ -3304,32 +3306,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[56.06, 60.5, 58.93]</t>
+          <t>[56.44, 57.77, 86.69]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[53.6, 51.9, 80.83]</t>
+          <t>[49.8, 48.0, 85.1]</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>13.65919823771045</v>
+        <v>6.880576017858368</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9866355731143</v>
+        <v>5.99801702302769</v>
       </c>
       <c r="H80" t="n">
-        <v>16.08393491978726</v>
+        <v>11.84904115460565</v>
       </c>
     </row>
     <row r="81">
@@ -3340,32 +3342,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[60.06, 58.5, 193.85]</t>
+          <t>[56.61, 84.99, 60.13]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[51.9, 80.83, 212.13]</t>
+          <t>[48.0, 85.1, 128.01]</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>17.31637675808157</v>
+        <v>39.50566813151571</v>
       </c>
       <c r="G81" t="n">
-        <v>16.25809918413555</v>
+        <v>25.5341316472461</v>
       </c>
       <c r="H81" t="n">
-        <v>17.32225705878599</v>
+        <v>23.69922603063339</v>
       </c>
     </row>
     <row r="82">
@@ -3376,32 +3378,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[1771.61, 1822.85, 2144.96]</t>
+          <t>[2405.18, 3085.72, 3896.43]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[1890.85, 1811.02, 2093.26]</t>
+          <t>[2216.19, 2803.71, 3650.97]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>75.34660955312037</v>
+        <v>241.8655801789754</v>
       </c>
       <c r="G82" t="n">
-        <v>60.92282118198887</v>
+        <v>238.8194837310521</v>
       </c>
       <c r="H82" t="n">
-        <v>3.143048695622457</v>
+        <v>8.436392291081303</v>
       </c>
     </row>
     <row r="83">
@@ -3412,32 +3414,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[1866.22, 2192.17, 1973.72]</t>
+          <t>[3009.66, 3803.12, 3950.67]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[1811.02, 2093.26, 2116.01]</t>
+          <t>[2803.71, 3650.97, 3782.45]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>105.0035037451603</v>
+        <v>176.8827018061618</v>
       </c>
       <c r="G83" t="n">
-        <v>98.80105131211788</v>
+        <v>175.4394036743285</v>
       </c>
       <c r="H83" t="n">
-        <v>4.832589694978486</v>
+        <v>5.320110723573503</v>
       </c>
     </row>
     <row r="84">
@@ -3448,32 +3450,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[2169.24, 1953.76, 2355.44]</t>
+          <t>[3713.75, 3859.11, 4504.09]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[2093.26, 2116.01, 2627.58]</t>
+          <t>[3650.97, 3782.45, 4695.5]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>188.1106239017893</v>
+        <v>124.4421974235697</v>
       </c>
       <c r="G84" t="n">
-        <v>170.122097473139</v>
+        <v>110.2857979686602</v>
       </c>
       <c r="H84" t="n">
-        <v>7.218128570855282</v>
+        <v>2.607637345029656</v>
       </c>
     </row>
     <row r="85">
@@ -3484,32 +3486,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[1929.76, 2326.89, 4564.3]</t>
+          <t>[3836.0, 4476.44, 1780.9]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[2116.01, 2627.58, 4815.7]</t>
+          <t>[3782.45, 4695.5, 1880.47]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>250.5355969549763</v>
+        <v>142.3225970799679</v>
       </c>
       <c r="G85" t="n">
-        <v>246.1124597910932</v>
+        <v>124.0580896662767</v>
       </c>
       <c r="H85" t="n">
-        <v>8.4886036379714</v>
+        <v>3.791922760525234</v>
       </c>
     </row>
     <row r="86">
@@ -3520,32 +3522,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[2402.47, 4712.87, 2548.01]</t>
+          <t>[4454.48, 1772.07, 1748.8]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[2627.58, 4815.7, 2443.5]</t>
+          <t>[4695.5, 1880.47, 1806.25]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>155.1018572918226</v>
+        <v>156.1420781441007</v>
       </c>
       <c r="G86" t="n">
-        <v>144.1475514556272</v>
+        <v>135.6234856503934</v>
       </c>
       <c r="H86" t="n">
-        <v>4.993120980139984</v>
+        <v>4.692738429402956</v>
       </c>
     </row>
     <row r="87">
@@ -3556,32 +3558,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[4857.28, 2623.98, 2474.06]</t>
+          <t>[1803.98, 1779.05, 2088.23]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[4815.7, 2443.5, 2216.19]</t>
+          <t>[1880.47, 1806.25, 2109.5]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>183.3028410883306</v>
+        <v>48.45243737589612</v>
       </c>
       <c r="G87" t="n">
-        <v>159.9770740924112</v>
+        <v>41.65223916225963</v>
       </c>
       <c r="H87" t="n">
-        <v>6.62844805669907</v>
+        <v>2.193878304374508</v>
       </c>
     </row>
     <row r="88">
@@ -3592,32 +3594,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[2616.22, 2466.61, 3158.51]</t>
+          <t>[1803.01, 2116.24, 2029.32]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[2443.5, 2216.19, 2803.71]</t>
+          <t>[1806.25, 2109.5, 2102.1]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>269.827765858493</v>
+        <v>42.24241461176248</v>
       </c>
       <c r="G88" t="n">
-        <v>259.3109807470078</v>
+        <v>27.58552733913446</v>
       </c>
       <c r="H88" t="n">
-        <v>10.34083022053757</v>
+        <v>1.320319022434053</v>
       </c>
     </row>
     <row r="89">
@@ -3628,32 +3630,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[2405.18, 3085.72, 3896.43]</t>
+          <t>[2117.53, 2030.38, 2447.21]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[2216.19, 2803.71, 3650.97]</t>
+          <t>[2109.5, 2102.1, 2455.4]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>241.8655801789754</v>
+        <v>41.93144428261538</v>
       </c>
       <c r="G89" t="n">
-        <v>238.8194837310521</v>
+        <v>29.31019120682928</v>
       </c>
       <c r="H89" t="n">
-        <v>8.436392291081303</v>
+        <v>1.375204352982153</v>
       </c>
     </row>
     <row r="90">
@@ -3664,32 +3666,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[3009.66, 3803.12, 3950.67]</t>
+          <t>[2027.99, 2444.41, 4589.77]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[2803.71, 3650.97, 3782.45]</t>
+          <t>[2102.1, 2455.4, 4804.0]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>176.8827018061618</v>
+        <v>131.0297033302438</v>
       </c>
       <c r="G90" t="n">
-        <v>175.4394036743285</v>
+        <v>99.77526739445732</v>
       </c>
       <c r="H90" t="n">
-        <v>5.320110723573503</v>
+        <v>2.81078620190204</v>
       </c>
     </row>
     <row r="91">
@@ -3700,32 +3702,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[3713.75, 3859.11, 4504.09]</t>
+          <t>[2476.12, 4643.35, 2433.73]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[3650.97, 3782.45, 4695.5]</t>
+          <t>[2455.4, 4804.0, 2430.85]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>124.4421974235697</v>
+        <v>93.53327939923034</v>
       </c>
       <c r="G91" t="n">
-        <v>110.2857979686602</v>
+        <v>61.41689520219249</v>
       </c>
       <c r="H91" t="n">
-        <v>2.607637345029656</v>
+        <v>1.435497997276974</v>
       </c>
     </row>
     <row r="92">
@@ -3736,32 +3738,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[575.63, 547.21, 974.35]</t>
+          <t>[1746.38, 1501.3, 1737.81]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[586.05, 603.01, 1030.75]</t>
+          <t>[1783.24, 1506.79, 1740.69]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>46.20023036229347</v>
+        <v>21.58013113937836</v>
       </c>
       <c r="G92" t="n">
-        <v>40.8728438731323</v>
+        <v>15.07770807127395</v>
       </c>
       <c r="H92" t="n">
-        <v>5.5010564522531</v>
+        <v>0.8656674714033686</v>
       </c>
     </row>
     <row r="93">
@@ -3772,32 +3774,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[549.32, 978.17, 1293.3]</t>
+          <t>[1508.32, 1745.98, 1645.14]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[603.01, 1030.75, 1328.7]</t>
+          <t>[1506.79, 1740.69, 1660.1]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>47.96020482098768</v>
+        <v>9.202100877727499</v>
       </c>
       <c r="G93" t="n">
-        <v>47.22372856960302</v>
+        <v>7.258550056542087</v>
       </c>
       <c r="H93" t="n">
-        <v>5.556381256590743</v>
+        <v>0.4354400154901812</v>
       </c>
     </row>
     <row r="94">
@@ -3808,32 +3810,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[998.48, 1320.35, 1537.98]</t>
+          <t>[1745.57, 1644.76, 3131.59]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[1030.75, 1328.7, 1579.88]</t>
+          <t>[1740.69, 1660.1, 3139.58]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>30.9141828153729</v>
+        <v>10.37505039739013</v>
       </c>
       <c r="G94" t="n">
-        <v>27.50983334246666</v>
+        <v>9.404015569136542</v>
       </c>
       <c r="H94" t="n">
-        <v>2.137363638601808</v>
+        <v>0.4863062930975792</v>
       </c>
     </row>
     <row r="95">
@@ -3844,32 +3846,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[1330.08, 1549.25, 2139.1]</t>
+          <t>[1643.71, 3129.57, 608.72]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[1328.7, 1579.88, 2165.38]</t>
+          <t>[1660.1, 3139.58, 595.67]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>23.31481175771318</v>
+        <v>13.40309844607584</v>
       </c>
       <c r="G95" t="n">
-        <v>19.42912037049571</v>
+        <v>13.14795862706137</v>
       </c>
       <c r="H95" t="n">
-        <v>1.085380818204843</v>
+        <v>1.165330463914231</v>
       </c>
     </row>
     <row r="96">
@@ -3880,32 +3882,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[1548.88, 2138.6, 1440.74]</t>
+          <t>[3136.6, 610.11, 610.8]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[1579.88, 2165.38, 1460.76]</t>
+          <t>[3139.58, 595.67, 629.36]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>26.32694145226648</v>
+        <v>13.6836051630781</v>
       </c>
       <c r="G96" t="n">
-        <v>25.93526067655193</v>
+        <v>11.99088823277339</v>
       </c>
       <c r="H96" t="n">
-        <v>1.523257638728775</v>
+        <v>1.822467303399267</v>
       </c>
     </row>
     <row r="97">
@@ -3916,32 +3918,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[2148.24, 1447.3, 1740.22]</t>
+          <t>[610.24, 610.93, 1042.33]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[2165.38, 1460.76, 1783.24]</t>
+          <t>[595.67, 629.36, 1093.13]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>27.84005684048327</v>
+        <v>32.31390823494227</v>
       </c>
       <c r="G97" t="n">
-        <v>24.53796277453186</v>
+        <v>27.93339703147387</v>
       </c>
       <c r="H97" t="n">
-        <v>1.375059985585209</v>
+        <v>3.340541880579079</v>
       </c>
     </row>
     <row r="98">
@@ -3952,32 +3954,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[1449.93, 1743.38, 1498.78]</t>
+          <t>[607.53, 1036.66, 1340.56]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[1460.76, 1783.24, 1506.79]</t>
+          <t>[629.36, 1093.13, 1348.0]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>24.29304476320092</v>
+        <v>35.2177804839525</v>
       </c>
       <c r="G98" t="n">
-        <v>19.56719243841705</v>
+        <v>28.58104671869739</v>
       </c>
       <c r="H98" t="n">
-        <v>1.169439532443214</v>
+        <v>3.062350468701613</v>
       </c>
     </row>
     <row r="99">
@@ -3988,32 +3990,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[1746.38, 1501.3, 1737.81]</t>
+          <t>[1045.01, 1351.13, 1596.78]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[1783.24, 1506.79, 1740.69]</t>
+          <t>[1093.13, 1348.0, 1610.72]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>21.58013113937836</v>
+        <v>28.9806009530158</v>
       </c>
       <c r="G99" t="n">
-        <v>15.07770807127395</v>
+        <v>21.7288007079491</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8656674714033686</v>
+        <v>1.833150862035796</v>
       </c>
     </row>
     <row r="100">
@@ -4024,32 +4026,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[1508.32, 1745.98, 1645.14]</t>
+          <t>[1365.0, 1613.17, 2209.0]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[1506.79, 1740.69, 1660.1]</t>
+          <t>[1348.0, 1610.72, 2238.47]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>9.202100877727499</v>
+        <v>19.69047447002976</v>
       </c>
       <c r="G100" t="n">
-        <v>7.258550056542087</v>
+        <v>16.30467584216581</v>
       </c>
       <c r="H100" t="n">
-        <v>0.4354400154901812</v>
+        <v>0.9098113905493697</v>
       </c>
     </row>
     <row r="101">
@@ -4060,32 +4062,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[1745.57, 1644.76, 3131.59]</t>
+          <t>[1608.59, 2202.73, 1483.59]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[1740.69, 1660.1, 3139.58]</t>
+          <t>[1610.72, 2238.47, 1548.44]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>10.37505039739013</v>
+        <v>42.76899484770163</v>
       </c>
       <c r="G101" t="n">
-        <v>9.404015569136542</v>
+        <v>34.23952248591468</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4863062930975792</v>
+        <v>1.972269474584067</v>
       </c>
     </row>
     <row r="102">
@@ -4096,32 +4098,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[362.46, 348.24, 763.71]</t>
+          <t>[840.79, 2577.77, 560.65]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[428.9, 459.13, 830.45]</t>
+          <t>[884.19, 2552.15, 492.32]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>83.99728518036275</v>
+        <v>49.02073379651896</v>
       </c>
       <c r="G102" t="n">
-        <v>81.35959011422851</v>
+        <v>45.78326489483726</v>
       </c>
       <c r="H102" t="n">
-        <v>15.89376466945339</v>
+        <v>6.597267154373466</v>
       </c>
     </row>
     <row r="103">
@@ -4132,32 +4134,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[368.14, 829.21, 377.4]</t>
+          <t>[2631.45, 572.08, 1158.97]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[459.13, 830.45, 372.29]</t>
+          <t>[2552.15, 492.32, 1099.66]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>52.62012236970382</v>
+        <v>73.41161586665294</v>
       </c>
       <c r="G103" t="n">
-        <v>32.44707145528696</v>
+        <v>72.78990154490424</v>
       </c>
       <c r="H103" t="n">
-        <v>7.113471081397011</v>
+        <v>8.2336279438126</v>
       </c>
     </row>
     <row r="104">
@@ -4168,32 +4170,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[910.13, 416.01, 1257.41]</t>
+          <t>[566.39, 1142.87, 2743.73]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[830.45, 372.29, 1133.94]</t>
+          <t>[492.32, 1099.66, 2551.96]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>88.51818578039446</v>
+        <v>121.2820511488306</v>
       </c>
       <c r="G104" t="n">
-        <v>82.29219225369503</v>
+        <v>103.0158852036523</v>
       </c>
       <c r="H104" t="n">
-        <v>10.74264164775651</v>
+        <v>8.829633608872401</v>
       </c>
     </row>
     <row r="105">
@@ -4204,32 +4206,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[398.98, 1209.81, 2060.14]</t>
+          <t>[1097.16, 2635.43, 410.38]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[372.29, 1133.94, 2052.66]</t>
+          <t>[1099.66, 2551.96, 381.0]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>46.63402882432722</v>
+        <v>51.10985218443545</v>
       </c>
       <c r="G105" t="n">
-        <v>36.67979207572242</v>
+        <v>38.4483432233258</v>
       </c>
       <c r="H105" t="n">
-        <v>4.741636066090484</v>
+        <v>3.736189502257015</v>
       </c>
     </row>
     <row r="106">
@@ -4240,32 +4242,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[1175.73, 2002.85, 573.32]</t>
+          <t>[2638.26, 410.81, 403.2]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[1133.94, 2052.66, 544.87]</t>
+          <t>[2551.96, 381.0, 375.04]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>40.97471168436442</v>
+        <v>55.1629839452069</v>
       </c>
       <c r="G106" t="n">
-        <v>40.01647301235164</v>
+        <v>48.08919352689016</v>
       </c>
       <c r="H106" t="n">
-        <v>3.777790237757567</v>
+        <v>6.238117914824672</v>
       </c>
     </row>
     <row r="107">
@@ -4276,32 +4278,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[1971.96, 565.74, 844.84]</t>
+          <t>[404.89, 396.99, 753.11]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[2052.66, 544.87, 884.19]</t>
+          <t>[381.0, 375.04, 837.54]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>53.21744306797324</v>
+        <v>52.21709140009533</v>
       </c>
       <c r="G107" t="n">
-        <v>46.97179690963401</v>
+        <v>43.41957410459477</v>
       </c>
       <c r="H107" t="n">
-        <v>4.070469919300821</v>
+        <v>7.400483490039406</v>
       </c>
     </row>
     <row r="108">
@@ -4312,32 +4314,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[574.11, 858.32, 2621.35]</t>
+          <t>[386.57, 734.14, 338.33]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[544.87, 884.19, 2552.15]</t>
+          <t>[375.04, 837.54, 357.73]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>45.87330970882763</v>
+        <v>61.10435389205443</v>
       </c>
       <c r="G108" t="n">
-        <v>41.43731464156895</v>
+        <v>44.7789933900178</v>
       </c>
       <c r="H108" t="n">
-        <v>3.668013494335496</v>
+        <v>6.948276403435043</v>
       </c>
     </row>
     <row r="109">
@@ -4348,32 +4350,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[840.79, 2577.77, 560.65]</t>
+          <t>[725.56, 334.52, 1035.25]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[884.19, 2552.15, 492.32]</t>
+          <t>[837.54, 357.73, 1127.95]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>49.02073379651896</v>
+        <v>84.99565626512886</v>
       </c>
       <c r="G109" t="n">
-        <v>45.78326489483726</v>
+        <v>75.965916694993</v>
       </c>
       <c r="H109" t="n">
-        <v>6.597267154373466</v>
+        <v>9.359308201920598</v>
       </c>
     </row>
     <row r="110">
@@ -4384,32 +4386,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[2631.45, 572.08, 1158.97]</t>
+          <t>[356.39, 1099.16, 1943.87]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[2552.15, 492.32, 1099.66]</t>
+          <t>[357.73, 1127.95, 2110.63]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>73.41161586665294</v>
+        <v>97.70403457388926</v>
       </c>
       <c r="G110" t="n">
-        <v>72.78990154490424</v>
+        <v>65.62887064018507</v>
       </c>
       <c r="H110" t="n">
-        <v>8.2336279438126</v>
+        <v>3.609160338563917</v>
       </c>
     </row>
     <row r="111">
@@ -4420,32 +4422,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[566.39, 1142.87, 2743.73]</t>
+          <t>[1100.89, 1946.81, 531.6]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[492.32, 1099.66, 2551.96]</t>
+          <t>[1127.95, 2110.63, 518.05]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>121.2820511488306</v>
+        <v>96.18391816024656</v>
       </c>
       <c r="G111" t="n">
-        <v>103.0158852036523</v>
+        <v>68.14234954623036</v>
       </c>
       <c r="H111" t="n">
-        <v>8.829633608872401</v>
+        <v>4.258512166715326</v>
       </c>
     </row>
     <row r="112">
@@ -4456,32 +4458,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[236.06, 112.48, 149.6]</t>
+          <t>[164.51, 209.66, 189.98]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[315.08, 133.21, 185.42]</t>
+          <t>[136.33, 155.72, 144.52]</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>51.49935581830965</v>
+        <v>43.85524292690827</v>
       </c>
       <c r="G112" t="n">
-        <v>45.1897785361088</v>
+        <v>42.52524055809052</v>
       </c>
       <c r="H112" t="n">
-        <v>19.98686167860875</v>
+        <v>28.92083257988208</v>
       </c>
     </row>
     <row r="113">
@@ -4492,32 +4494,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[142.15, 188.55, 1469.64]</t>
+          <t>[184.67, 167.51, 546.76]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>[133.21, 185.42, 1381.39]</t>
+          <t>[155.72, 144.52, 434.93]</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>51.2459504958385</v>
+        <v>68.00433182538259</v>
       </c>
       <c r="G113" t="n">
-        <v>33.43971930997898</v>
+        <v>54.59337040831104</v>
       </c>
       <c r="H113" t="n">
-        <v>4.928388489422639</v>
+        <v>20.07205662559048</v>
       </c>
     </row>
     <row r="114">
@@ -4528,32 +4530,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[179.42, 1399.48, 82.15]</t>
+          <t>[147.1, 480.95, 548.57]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[185.42, 1381.39, 95.65]</t>
+          <t>[144.52, 434.93, 440.47]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>13.48625278818852</v>
+        <v>67.84617517792313</v>
       </c>
       <c r="G114" t="n">
-        <v>12.53133934552772</v>
+        <v>52.23165262572365</v>
       </c>
       <c r="H114" t="n">
-        <v>6.220284154997178</v>
+        <v>12.30215797002218</v>
       </c>
     </row>
     <row r="115">
@@ -4564,32 +4566,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[1433.98, 84.17, 109.98]</t>
+          <t>[474.51, 541.29, 276.15]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[1381.39, 95.65, 182.41]</t>
+          <t>[434.93, 440.47, 330.86]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>52.09968916491931</v>
+        <v>70.05845441102713</v>
       </c>
       <c r="G115" t="n">
-        <v>45.49776586556135</v>
+        <v>65.03796120052704</v>
       </c>
       <c r="H115" t="n">
-        <v>18.50303173824797</v>
+        <v>16.17546196127547</v>
       </c>
     </row>
     <row r="116">
@@ -4600,32 +4602,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[81.85, 106.97, 150.87]</t>
+          <t>[506.71, 258.64, 121.72]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[95.65, 182.41, 178.03]</t>
+          <t>[440.47, 330.86, 141.87]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>46.97233397754556</v>
+        <v>57.76603050630979</v>
       </c>
       <c r="G116" t="n">
-        <v>38.80178361847152</v>
+        <v>52.87400912444787</v>
       </c>
       <c r="H116" t="n">
-        <v>23.68190704659004</v>
+        <v>17.02483477999349</v>
       </c>
     </row>
     <row r="117">
@@ -4636,32 +4638,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[119.91, 168.91, 145.09]</t>
+          <t>[231.81, 109.13, 145.85]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[182.41, 178.03, 136.33]</t>
+          <t>[330.86, 141.87, 179.06]</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>36.81393207095654</v>
+        <v>63.2055778185393</v>
       </c>
       <c r="G117" t="n">
-        <v>26.79413005008029</v>
+        <v>54.9969691119821</v>
       </c>
       <c r="H117" t="n">
-        <v>15.27126657950144</v>
+        <v>23.85209059699772</v>
       </c>
     </row>
     <row r="118">
@@ -4672,32 +4674,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[242.42, 207.65, 264.02]</t>
+          <t>[128.87, 184.43, 1441.83]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[178.03, 136.33, 155.72]</t>
+          <t>[141.87, 179.06, 1433.99]</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>83.58775378681318</v>
+        <v>9.295315279939601</v>
       </c>
       <c r="G118" t="n">
-        <v>81.33537508801196</v>
+        <v>8.734838610854098</v>
       </c>
       <c r="H118" t="n">
-        <v>52.67570234156045</v>
+        <v>4.2360279776848</v>
       </c>
     </row>
     <row r="119">
@@ -4708,32 +4710,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[164.51, 209.66, 189.98]</t>
+          <t>[198.16, 1543.3, 97.79]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[136.33, 155.72, 144.52]</t>
+          <t>[179.06, 1433.99, 149.31]</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>43.85524292690827</v>
+        <v>70.63526924062145</v>
       </c>
       <c r="G119" t="n">
-        <v>42.52524055809052</v>
+        <v>59.9765896024148</v>
       </c>
       <c r="H119" t="n">
-        <v>28.92083257988208</v>
+        <v>17.5980841887028</v>
       </c>
     </row>
     <row r="120">
@@ -4744,32 +4746,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[184.67, 167.51, 546.76]</t>
+          <t>[1444.96, 92.17, 131.08]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[155.72, 144.52, 434.93]</t>
+          <t>[1433.99, 149.31, 133.92]</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>68.00433182538259</v>
+        <v>33.63010739798278</v>
       </c>
       <c r="G120" t="n">
-        <v>54.59337040831104</v>
+        <v>23.64793646619782</v>
       </c>
       <c r="H120" t="n">
-        <v>20.07205662559048</v>
+        <v>13.71660992826068</v>
       </c>
     </row>
     <row r="121">
@@ -4780,32 +4782,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[147.1, 480.95, 548.57]</t>
+          <t>[91.67, 130.27, 143.91]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[144.52, 434.93, 440.47]</t>
+          <t>[149.31, 133.92, 153.09]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>67.84617517792313</v>
+        <v>33.7651438324007</v>
       </c>
       <c r="G121" t="n">
-        <v>52.23165262572365</v>
+        <v>23.48904563475854</v>
       </c>
       <c r="H121" t="n">
-        <v>12.30215797002218</v>
+        <v>15.77465170589832</v>
       </c>
     </row>
     <row r="122">
@@ -4816,32 +4818,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[446.93, 432.55, 393.93]</t>
+          <t>[571.84, 461.3, 476.53]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[535.11, 473.04, 450.3]</t>
+          <t>[709.2, 579.41, 590.55]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>64.78911212035418</v>
+        <v>123.5830392998766</v>
       </c>
       <c r="G122" t="n">
-        <v>61.68017284754279</v>
+        <v>123.1633213674304</v>
       </c>
       <c r="H122" t="n">
-        <v>12.51895969121309</v>
+        <v>19.68674749198983</v>
       </c>
     </row>
     <row r="123">
@@ -4852,32 +4854,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[466.57, 423.71, 428.96]</t>
+          <t>[525.99, 539.69, 472.7]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[473.04, 450.3, 508.6]</t>
+          <t>[579.41, 590.55, 550.88]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>48.61837588962453</v>
+        <v>62.0541233135908</v>
       </c>
       <c r="G123" t="n">
-        <v>37.56719898687087</v>
+        <v>60.81946444567232</v>
       </c>
       <c r="H123" t="n">
-        <v>7.643918821158858</v>
+        <v>10.6745145019404</v>
       </c>
     </row>
     <row r="124">
@@ -4888,32 +4890,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[426.67, 431.9, 629.71]</t>
+          <t>[560.08, 491.5, 667.41]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[450.3, 508.6, 591.8]</t>
+          <t>[590.55, 550.88, 544.11]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>51.24511297569385</v>
+        <v>80.94830083295257</v>
       </c>
       <c r="G124" t="n">
-        <v>46.07996002459506</v>
+        <v>71.05078555871897</v>
       </c>
       <c r="H124" t="n">
-        <v>8.911423108678072</v>
+        <v>12.86667938825195</v>
       </c>
     </row>
     <row r="125">
@@ -4924,32 +4926,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[442.49, 645.76, 661.24]</t>
+          <t>[500.18, 679.22, 486.71]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[508.6, 591.8, 617.25]</t>
+          <t>[550.88, 544.11, 533.78]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>55.43270845920836</v>
+        <v>87.63465296689002</v>
       </c>
       <c r="G125" t="n">
-        <v>54.68992367517592</v>
+        <v>77.62458393998332</v>
       </c>
       <c r="H125" t="n">
-        <v>9.748275018047641</v>
+        <v>14.28396941342346</v>
       </c>
     </row>
     <row r="126">
@@ -4960,32 +4962,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[688.78, 703.91, 623.81]</t>
+          <t>[700.07, 501.65, 453.89]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[591.8, 617.25, 352.14]</t>
+          <t>[544.11, 533.78, 474.22]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>173.8975126659919</v>
+        <v>92.68005568144882</v>
       </c>
       <c r="G126" t="n">
-        <v>151.7695768122643</v>
+        <v>69.47367336327238</v>
       </c>
       <c r="H126" t="n">
-        <v>35.85853217962301</v>
+        <v>12.98998108042925</v>
       </c>
     </row>
     <row r="127">
@@ -4996,32 +4998,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[658.4, 584.02, 764.83]</t>
+          <t>[466.91, 422.82, 388.83]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[617.25, 352.14, 709.2]</t>
+          <t>[533.78, 474.22, 443.29]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>139.7077389818317</v>
+        <v>57.96558188226494</v>
       </c>
       <c r="G127" t="n">
-        <v>109.5520169816844</v>
+        <v>57.57813692408374</v>
       </c>
       <c r="H127" t="n">
-        <v>26.78613792431834</v>
+        <v>11.88422573719552</v>
       </c>
     </row>
     <row r="128">
@@ -5032,32 +5034,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[568.85, 745.29, 598.22]</t>
+          <t>[439.76, 404.32, 423.55]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[352.14, 709.2, 579.41]</t>
+          <t>[474.22, 443.29, 309.81]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>127.3046017304699</v>
+        <v>72.20888361455548</v>
       </c>
       <c r="G128" t="n">
-        <v>90.5368191651941</v>
+        <v>62.38899638955146</v>
       </c>
       <c r="H128" t="n">
-        <v>23.29207489998816</v>
+        <v>17.58988653871825</v>
       </c>
     </row>
     <row r="129">
@@ -5068,32 +5070,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[571.84, 461.3, 476.53]</t>
+          <t>[411.57, 431.12, 562.16]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[709.2, 579.41, 590.55]</t>
+          <t>[443.29, 309.81, 628.26]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>123.5830392998766</v>
+        <v>81.83702676931954</v>
       </c>
       <c r="G129" t="n">
-        <v>123.1633213674304</v>
+        <v>73.0452455326981</v>
       </c>
       <c r="H129" t="n">
-        <v>19.68674749198983</v>
+        <v>18.94469719817843</v>
       </c>
     </row>
     <row r="130">
@@ -5104,32 +5106,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[525.99, 539.69, 472.7]</t>
+          <t>[438.63, 571.85, 600.09]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[579.41, 590.55, 550.88]</t>
+          <t>[309.81, 628.26, 526.68]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>62.0541233135908</v>
+        <v>91.58896462664917</v>
       </c>
       <c r="G130" t="n">
-        <v>60.81946444567232</v>
+        <v>86.21341132069858</v>
       </c>
       <c r="H130" t="n">
-        <v>10.6745145019404</v>
+        <v>21.49907573537223</v>
       </c>
     </row>
     <row r="131">
@@ -5140,32 +5142,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[560.08, 491.5, 667.41]</t>
+          <t>[533.07, 560.07, 431.52]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[590.55, 550.88, 544.11]</t>
+          <t>[628.26, 526.68, 250.73]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>80.94830083295257</v>
+        <v>119.5282013663372</v>
       </c>
       <c r="G131" t="n">
-        <v>71.05078555871897</v>
+        <v>103.1248748407263</v>
       </c>
       <c r="H131" t="n">
-        <v>12.86667938825195</v>
+        <v>31.19888451032973</v>
       </c>
     </row>
     <row r="132">
@@ -5176,32 +5178,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[161.51, 182.66, 94.77]</t>
+          <t>[227.37, 481.99, 336.18]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>[169.4, 192.02, 107.68]</t>
+          <t>[215.64, 452.73, 308.4]</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>10.26952093984719</v>
+        <v>24.25999933739047</v>
       </c>
       <c r="G132" t="n">
-        <v>10.05126831535134</v>
+        <v>22.92499664142967</v>
       </c>
       <c r="H132" t="n">
-        <v>7.172175694111516</v>
+        <v>6.970691365448868</v>
       </c>
     </row>
     <row r="133">
@@ -5212,32 +5214,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[183.31, 95.1, 52.84]</t>
+          <t>[479.92, 334.78, 290.45]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>[192.02, 107.68, 81.6]</t>
+          <t>[452.73, 308.4, 277.6]</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>18.80850310593077</v>
+        <v>23.09508434891518</v>
       </c>
       <c r="G133" t="n">
-        <v>16.68273261702143</v>
+        <v>22.13827104278715</v>
       </c>
       <c r="H133" t="n">
-        <v>17.15445062871881</v>
+        <v>6.395681835425266</v>
       </c>
     </row>
     <row r="134">
@@ -5248,32 +5250,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[95.41, 53.01, 144.56]</t>
+          <t>[333.4, 289.28, 364.35]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>[107.68, 81.6, 139.45]</t>
+          <t>[308.4, 277.6, 351.2]</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>18.20678047116045</v>
+        <v>17.64701880800977</v>
       </c>
       <c r="G134" t="n">
-        <v>15.32768183531038</v>
+        <v>16.60985987666188</v>
       </c>
       <c r="H134" t="n">
-        <v>16.70284683070257</v>
+        <v>5.352657553306636</v>
       </c>
     </row>
     <row r="135">
@@ -5284,32 +5286,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[53.44, 145.72, 250.94]</t>
+          <t>[287.84, 362.54, 171.99]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[81.6, 139.45, 245.63]</t>
+          <t>[277.6, 351.2, 151.54]</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>16.93809316864885</v>
+        <v>14.74034140173918</v>
       </c>
       <c r="G135" t="n">
-        <v>13.24805677562458</v>
+        <v>14.01268103763532</v>
       </c>
       <c r="H135" t="n">
-        <v>13.72420831752091</v>
+        <v>6.805047910456878</v>
       </c>
     </row>
     <row r="136">
@@ -5320,32 +5322,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[150.76, 260.0, 222.98]</t>
+          <t>[361.74, 171.59, 193.98]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>[139.45, 245.63, 209.97]</t>
+          <t>[351.2, 151.54, 157.54]</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>12.95990095934635</v>
+        <v>24.7743593497074</v>
       </c>
       <c r="G136" t="n">
-        <v>12.89933471741466</v>
+        <v>22.34550676642083</v>
       </c>
       <c r="H136" t="n">
-        <v>6.720414891312858</v>
+        <v>13.1220245161003</v>
       </c>
     </row>
     <row r="137">
@@ -5356,32 +5358,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[257.53, 220.86, 229.62]</t>
+          <t>[171.29, 193.64, 107.8]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>[245.63, 209.97, 215.64]</t>
+          <t>[151.54, 157.54, 131.34]</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>12.3232943087883</v>
+        <v>27.3700077452529</v>
       </c>
       <c r="G137" t="n">
-        <v>12.25599384351766</v>
+        <v>26.46266526297255</v>
       </c>
       <c r="H137" t="n">
-        <v>5.504449111020839</v>
+        <v>17.95649004017297</v>
       </c>
     </row>
     <row r="138">
@@ -5392,32 +5394,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[219.7, 228.39, 483.91]</t>
+          <t>[192.12, 106.89, 78.76]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>[209.97, 215.64, 452.73]</t>
+          <t>[157.54, 131.34, 51.12]</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>20.24249841129411</v>
+        <v>29.19715950288311</v>
       </c>
       <c r="G138" t="n">
-        <v>17.88609836875169</v>
+        <v>28.88945327197014</v>
       </c>
       <c r="H138" t="n">
-        <v>5.811180597215607</v>
+        <v>31.54574040051052</v>
       </c>
     </row>
     <row r="139">
@@ -5428,32 +5430,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[227.37, 481.99, 336.18]</t>
+          <t>[105.29, 77.26, 133.8]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[215.64, 452.73, 308.4]</t>
+          <t>[131.34, 51.12, 132.39]</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>24.25999933739047</v>
+        <v>21.32171556602314</v>
       </c>
       <c r="G139" t="n">
-        <v>22.92499664142967</v>
+        <v>17.86690215106888</v>
       </c>
       <c r="H139" t="n">
-        <v>6.970691365448868</v>
+        <v>24.01123663229467</v>
       </c>
     </row>
     <row r="140">
@@ -5464,32 +5466,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[479.92, 334.78, 290.45]</t>
+          <t>[79.33, 136.09, 240.25]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[452.73, 308.4, 277.6]</t>
+          <t>[51.12, 132.39, 207.71]</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>23.09508434891518</v>
+        <v>24.95487319628758</v>
       </c>
       <c r="G140" t="n">
-        <v>22.13827104278715</v>
+        <v>21.48329610344417</v>
       </c>
       <c r="H140" t="n">
-        <v>6.395681835425266</v>
+        <v>24.54710305633338</v>
       </c>
     </row>
     <row r="141">
@@ -5500,32 +5502,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[333.4, 289.28, 364.35]</t>
+          <t>[131.63, 232.57, 199.62]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>[308.4, 277.6, 351.2]</t>
+          <t>[132.39, 207.71, 176.88]</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>17.64701880800977</v>
+        <v>19.45411587638349</v>
       </c>
       <c r="G141" t="n">
-        <v>16.60985987666188</v>
+        <v>16.11761790512098</v>
       </c>
       <c r="H141" t="n">
-        <v>5.352657553306636</v>
+        <v>8.46500835368113</v>
       </c>
     </row>
     <row r="142">
@@ -5536,32 +5538,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[3927.53, 1775.91, 1841.66]</t>
+          <t>[1831.87, 1686.2, 1435.55]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[3918.02, 1766.04, 1823.93]</t>
+          <t>[1823.93, 1726.94, 1366.53]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>12.93888682415787</v>
+        <v>46.50273554523861</v>
       </c>
       <c r="G142" t="n">
-        <v>12.37017434710704</v>
+        <v>39.23595147048892</v>
       </c>
       <c r="H142" t="n">
-        <v>0.59120372281651</v>
+        <v>2.61522755384811</v>
       </c>
     </row>
     <row r="143">
@@ -5572,32 +5574,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[1771.61, 1837.18, 1690.85]</t>
+          <t>[1679.15, 1429.85, 1910.36]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[1766.04, 1823.93, 1726.94]</t>
+          <t>[1726.94, 1366.53, 1920.41]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>22.42541941777593</v>
+        <v>46.17032609017566</v>
       </c>
       <c r="G143" t="n">
-        <v>18.30187498439765</v>
+        <v>40.38914223705698</v>
       </c>
       <c r="H143" t="n">
-        <v>1.043808572185685</v>
+        <v>2.641587663077489</v>
       </c>
     </row>
     <row r="144">
@@ -5608,32 +5610,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[1831.87, 1686.2, 1435.55]</t>
+          <t>[1469.28, 1961.44, 6311.88]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[1823.93, 1726.94, 1366.53]</t>
+          <t>[1366.53, 1920.41, 5726.09]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>46.50273554523861</v>
+        <v>344.1841354736368</v>
       </c>
       <c r="G144" t="n">
-        <v>39.23595147048892</v>
+        <v>243.1895387895893</v>
       </c>
       <c r="H144" t="n">
-        <v>2.61522755384811</v>
+        <v>6.628631052720745</v>
       </c>
     </row>
     <row r="145">
@@ -5644,32 +5646,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[1679.15, 1429.85, 1910.36]</t>
+          <t>[1828.45, 5897.21, 547.96]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[1726.94, 1366.53, 1920.41]</t>
+          <t>[1920.41, 5726.09, 612.23]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>46.17032609017566</v>
+        <v>118.1368213829796</v>
       </c>
       <c r="G145" t="n">
-        <v>40.38914223705698</v>
+        <v>109.1169894933945</v>
       </c>
       <c r="H145" t="n">
-        <v>2.641587663077489</v>
+        <v>6.09163947336233</v>
       </c>
     </row>
     <row r="146">
@@ -5680,1472 +5682,2012 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[1469.28, 1961.44, 6311.88]</t>
+          <t>[6184.34, 573.79, 838.96]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[1366.53, 1920.41, 5726.09]</t>
+          <t>[5726.09, 612.23, 873.95]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>344.1841354736368</v>
+        <v>266.2702901023599</v>
       </c>
       <c r="G146" t="n">
-        <v>243.1895387895893</v>
+        <v>177.2285368504712</v>
       </c>
       <c r="H146" t="n">
-        <v>6.628631052720745</v>
+        <v>6.095082734145559</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[3690.28, 711.46, 1510.21]</t>
+          <t>[532.58, 780.76, 1092.4]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[3743.56, 719.87, 1529.73]</t>
+          <t>[612.23, 873.95, 1305.68]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>33.11752763525879</v>
+        <v>142.0293846982837</v>
       </c>
       <c r="G147" t="n">
-        <v>27.06928851888119</v>
+        <v>128.7075936818716</v>
       </c>
       <c r="H147" t="n">
-        <v>1.289183040759273</v>
+        <v>13.33602718844126</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[717.11, 1521.64, 2615.26]</t>
+          <t>[893.13, 1243.73, 1721.81]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[719.87, 1529.73, 2717.96]</t>
+          <t>[873.95, 1305.68, 1741.28]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>59.50137632411358</v>
+        <v>39.09626986718471</v>
       </c>
       <c r="G148" t="n">
-        <v>37.85087106680468</v>
+        <v>33.5366108488652</v>
       </c>
       <c r="H148" t="n">
-        <v>1.563675883214336</v>
+        <v>2.686059086676761</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[1524.35, 2619.82, 2748.44]</t>
+          <t>[1217.87, 1687.18, 1738.61]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[1529.73, 2717.96, 2720.57]</t>
+          <t>[1305.68, 1741.28, 2006.25]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>58.98489599950698</v>
+        <v>165.596529401461</v>
       </c>
       <c r="G149" t="n">
-        <v>43.79810408257003</v>
+        <v>136.5146130791717</v>
       </c>
       <c r="H149" t="n">
-        <v>1.662386750001818</v>
+        <v>7.724012738184529</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[2623.53, 2752.39, 2779.89]</t>
+          <t>[1804.08, 1854.21, 4311.38]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[2717.96, 2720.57, 2738.85]</t>
+          <t>[1741.28, 2006.25, 4668.04]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>62.21926612382146</v>
+        <v>226.7643545600199</v>
       </c>
       <c r="G150" t="n">
-        <v>55.76204811767457</v>
+        <v>190.4997337659718</v>
       </c>
       <c r="H150" t="n">
-        <v>2.047401015251702</v>
+        <v>6.275099558744944</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[2798.16, 2824.19, 6943.52]</t>
+          <t>[1792.09, 4172.75, 1881.72]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[2720.57, 2738.85, 6680.27]</t>
+          <t>[2006.25, 4668.04, 1030.78]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>165.9365865825505</v>
+        <v>581.7391722602832</v>
       </c>
       <c r="G151" t="n">
-        <v>142.0601687731044</v>
+        <v>520.1254739576544</v>
       </c>
       <c r="H151" t="n">
-        <v>3.302849184987023</v>
+        <v>34.61237650427736</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[749.71, 243.09, 465.97]</t>
+          <t>[1524.35, 2619.82, 2748.44]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[801.55, 247.1, 521.6]</t>
+          <t>[1529.73, 2717.96, 2720.57]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>43.96425688265744</v>
+        <v>58.98489599950698</v>
       </c>
       <c r="G152" t="n">
-        <v>37.16181826125656</v>
+        <v>43.79810408257003</v>
       </c>
       <c r="H152" t="n">
-        <v>6.252348019487799</v>
+        <v>1.662386750001818</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[243.08, 465.95, 1191.32]</t>
+          <t>[2623.53, 2752.39, 2779.89]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[247.1, 521.6, 1111.5]</t>
+          <t>[2717.96, 2720.57, 2738.85]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>56.22361016707264</v>
+        <v>62.21926612382146</v>
       </c>
       <c r="G153" t="n">
-        <v>46.49411789508064</v>
+        <v>55.76204811767457</v>
       </c>
       <c r="H153" t="n">
-        <v>6.492056613676955</v>
+        <v>2.047401015251702</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[465.95, 1191.3, 635.75]</t>
+          <t>[2798.16, 2824.19, 6943.52]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[521.6, 1111.5, 617.6]</t>
+          <t>[2720.57, 2738.85, 6680.27]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>57.14005770757437</v>
+        <v>165.9365865825505</v>
       </c>
       <c r="G154" t="n">
-        <v>51.20098085858859</v>
+        <v>142.0601687731044</v>
       </c>
       <c r="H154" t="n">
-        <v>6.929236890219849</v>
+        <v>3.302849184987023</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[1191.33, 635.76, 417.2]</t>
+          <t>[2787.91, 6855.84, 700.86]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[1111.5, 617.6, 317.0]</t>
+          <t>[2738.85, 6680.27, 689.58]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>74.70197521640593</v>
+        <v>105.4520117986451</v>
       </c>
       <c r="G155" t="n">
-        <v>66.06047621366299</v>
+        <v>78.63692361330281</v>
       </c>
       <c r="H155" t="n">
-        <v>13.90990837063547</v>
+        <v>2.01831656346208</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[635.71, 417.18, 651.67]</t>
+          <t>[6800.98, 695.49, 712.7]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[617.6, 317.0, 441.06]</t>
+          <t>[6680.27, 689.58, 634.31]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>135.0569794078349</v>
+        <v>83.16672191628318</v>
       </c>
       <c r="G156" t="n">
-        <v>109.6338792759044</v>
+        <v>68.33636896034723</v>
       </c>
       <c r="H156" t="n">
-        <v>27.42872739866612</v>
+        <v>5.007427911241638</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[382.95, 412.73, 536.02]</t>
+          <t>[689.85, 707.14, 2974.89]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[351.38, 419.37, 514.38]</t>
+          <t>[689.58, 634.31, 3323.46]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>22.42798206884117</v>
+        <v>205.5939211482556</v>
       </c>
       <c r="G157" t="n">
-        <v>19.94855134810134</v>
+        <v>140.5570608232992</v>
       </c>
       <c r="H157" t="n">
-        <v>4.924679267306313</v>
+        <v>7.336337767449963</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[407.71, 529.98, 843.5]</t>
+          <t>[707.03, 2974.15, 834.38]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[419.37, 514.38, 899.78]</t>
+          <t>[634.31, 3323.46, 811.68]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>34.38319260939232</v>
+        <v>206.4137119418089</v>
       </c>
       <c r="G158" t="n">
-        <v>27.84646510086533</v>
+        <v>148.2446145890387</v>
       </c>
       <c r="H158" t="n">
-        <v>4.022645125201735</v>
+        <v>8.257436888315118</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[532.02, 846.49, 818.13]</t>
+          <t>[2828.16, 794.8, 549.64]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[514.38, 899.78, 774.78]</t>
+          <t>[3323.46, 811.68, 643.8]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>40.94677288683846</v>
+        <v>291.2488311773307</v>
       </c>
       <c r="G159" t="n">
-        <v>38.09168940193198</v>
+        <v>202.1162990329468</v>
       </c>
       <c r="H159" t="n">
-        <v>4.982084448299337</v>
+        <v>10.53637081687743</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[842.96, 814.62, 1087.95]</t>
+          <t>[844.11, 582.15, 3751.68]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[899.78, 774.78, 1138.67]</t>
+          <t>[811.68, 643.8, 4021.84]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>49.62528777074124</v>
+        <v>161.0806207458573</v>
       </c>
       <c r="G160" t="n">
-        <v>49.12618922385351</v>
+        <v>121.416340271088</v>
       </c>
       <c r="H160" t="n">
-        <v>5.303768661208633</v>
+        <v>6.763228676864708</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[821.19, 1096.76, 540.85]</t>
+          <t>[575.1, 3712.29, 714.7]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[774.78, 1138.67, 537.89]</t>
+          <t>[643.8, 4021.84, 801.79]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>36.14262202671309</v>
+        <v>189.8457390385963</v>
       </c>
       <c r="G161" t="n">
-        <v>30.42438924751389</v>
+        <v>155.1113441204681</v>
       </c>
       <c r="H161" t="n">
-        <v>3.406635549369146</v>
+        <v>9.742983149411288</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[1089.0, 536.98, 765.07]</t>
+          <t>[465.95, 1191.3, 635.75]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[1138.67, 537.89, 799.28]</t>
+          <t>[521.6, 1111.5, 617.6]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>34.82505608770235</v>
+        <v>57.14005770757437</v>
       </c>
       <c r="G162" t="n">
-        <v>28.26496852463629</v>
+        <v>51.20098085858859</v>
       </c>
       <c r="H162" t="n">
-        <v>2.937415350381986</v>
+        <v>6.929236890219849</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[539.93, 769.29, 942.19]</t>
+          <t>[1191.33, 635.76, 417.2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[537.89, 799.28, 949.76]</t>
+          <t>[1111.5, 617.6, 317.0]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>17.89926570014286</v>
+        <v>74.70197521640593</v>
       </c>
       <c r="G163" t="n">
-        <v>13.20042878793932</v>
+        <v>66.06047621366299</v>
       </c>
       <c r="H163" t="n">
-        <v>1.642780775739332</v>
+        <v>13.90990837063547</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[768.93, 941.75, 718.78]</t>
+          <t>[635.71, 417.18, 651.67]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[799.28, 949.76, 711.61]</t>
+          <t>[617.6, 317.0, 441.06]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>18.58917052366967</v>
+        <v>135.0569794078349</v>
       </c>
       <c r="G164" t="n">
-        <v>15.17615486066578</v>
+        <v>109.6338792759044</v>
       </c>
       <c r="H164" t="n">
-        <v>1.882684866610664</v>
+        <v>27.42872739866612</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[946.26, 722.18, 891.44]</t>
+          <t>[417.18, 651.62, 354.23]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[949.76, 711.61, 916.89]</t>
+          <t>[317.0, 441.06, 338.6]</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>16.03674953393003</v>
+        <v>134.9249925546788</v>
       </c>
       <c r="G165" t="n">
-        <v>13.17250807499007</v>
+        <v>108.7893111691107</v>
       </c>
       <c r="H165" t="n">
-        <v>1.543092157374836</v>
+        <v>27.98584767022313</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[722.51, 891.85, 1401.29]</t>
+          <t>[651.7, 354.27, 216.97]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[711.61, 916.89, 1525.3]</t>
+          <t>[441.06, 338.6, 294.8]</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>73.31376517403596</v>
+        <v>129.9668736708426</v>
       </c>
       <c r="G166" t="n">
-        <v>53.31612284782167</v>
+        <v>101.3831009194182</v>
       </c>
       <c r="H166" t="n">
-        <v>4.130834435134847</v>
+        <v>26.26306229281711</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[296.9, 43.16, 197.81]</t>
+          <t>[354.28, 216.94, 332.24]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[299.48, 54.71, 200.2]</t>
+          <t>[338.6, 294.8, 306.9]</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>6.969687051068599</v>
+        <v>48.1316581121223</v>
       </c>
       <c r="G167" t="n">
-        <v>5.506051047898642</v>
+        <v>39.62629718538501</v>
       </c>
       <c r="H167" t="n">
-        <v>7.721375482018819</v>
+        <v>13.09946705934646</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[43.25, 198.2, 329.46]</t>
+          <t>[216.93, 332.25, 263.64]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[54.71, 200.2, 285.56]</t>
+          <t>[294.8, 306.9, 261.8]</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>26.22068626952211</v>
+        <v>47.29303006994736</v>
       </c>
       <c r="G168" t="n">
-        <v>19.12064864974009</v>
+        <v>35.0210404056642</v>
       </c>
       <c r="H168" t="n">
-        <v>12.44157031530602</v>
+        <v>11.79287449419177</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[209.94, 349.1, 481.22]</t>
+          <t>[332.25, 263.64, 701.73]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[200.2, 285.56, 400.74]</t>
+          <t>[306.9, 261.8, 699.0]</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>59.46711625317491</v>
+        <v>14.75813272342264</v>
       </c>
       <c r="G169" t="n">
-        <v>51.25207982017664</v>
+        <v>9.972666347332583</v>
       </c>
       <c r="H169" t="n">
-        <v>15.73251247119932</v>
+        <v>3.117691095576973</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[344.15, 474.53, 504.57]</t>
+          <t>[263.66, 701.73, 766.59]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[285.56, 400.74, 470.6]</t>
+          <t>[261.8, 699.0, 794.2]</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>57.82631789158312</v>
+        <v>16.05411639434866</v>
       </c>
       <c r="G170" t="n">
-        <v>55.44924878016186</v>
+        <v>10.73063605154942</v>
       </c>
       <c r="H170" t="n">
-        <v>15.38308586620987</v>
+        <v>1.525079191305999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[455.06, 484.03, 1000.45]</t>
+          <t>[701.8, 766.67, 244.43]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[400.74, 470.6, 946.59]</t>
+          <t>[699.0, 794.2, 246.9]</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>44.84239805236876</v>
+        <v>16.0393824086576</v>
       </c>
       <c r="G171" t="n">
-        <v>40.53848646949573</v>
+        <v>10.93475216656272</v>
       </c>
       <c r="H171" t="n">
-        <v>7.366454577095177</v>
+        <v>1.622930247564166</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[473.34, 978.57, 1492.16]</t>
+          <t>[768.93, 941.75, 718.78]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[470.6, 946.59, 1452.09]</t>
+          <t>[799.28, 949.76, 711.61]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>29.64400627613182</v>
+        <v>18.58917052366967</v>
       </c>
       <c r="G172" t="n">
-        <v>24.931375596499</v>
+        <v>15.17615486066578</v>
       </c>
       <c r="H172" t="n">
-        <v>2.240061968305021</v>
+        <v>1.882684866610664</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[977.61, 1490.69, 696.38]</t>
+          <t>[946.26, 722.18, 891.44]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[946.59, 1452.09, 692.96]</t>
+          <t>[949.76, 711.61, 916.89]</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>28.65613315430696</v>
+        <v>16.03674953393003</v>
       </c>
       <c r="G173" t="n">
-        <v>24.3436283879865</v>
+        <v>13.17250807499007</v>
       </c>
       <c r="H173" t="n">
-        <v>2.14259740100387</v>
+        <v>1.543092157374836</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[1482.83, 692.69, 235.66]</t>
+          <t>[722.51, 891.85, 1401.29]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[1452.09, 692.96, 259.97]</t>
+          <t>[711.61, 916.89, 1525.3]</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>22.62675699860857</v>
+        <v>73.31376517403596</v>
       </c>
       <c r="G174" t="n">
-        <v>18.440680355071</v>
+        <v>53.31612284782167</v>
       </c>
       <c r="H174" t="n">
-        <v>3.836238819377622</v>
+        <v>4.130834435134847</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[690.06, 234.65, 244.6]</t>
+          <t>[890.2, 1398.71, 364.55]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[692.96, 259.97, 282.85]</t>
+          <t>[916.89, 1525.3, 392.03]</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>26.53782560060504</v>
+        <v>76.35789377319027</v>
       </c>
       <c r="G175" t="n">
-        <v>22.15599704006972</v>
+        <v>60.25095369910425</v>
       </c>
       <c r="H175" t="n">
-        <v>7.893828411026103</v>
+        <v>6.072971095570844</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[234.85, 244.8, 420.54]</t>
+          <t>[1403.86, 365.85, 419.08]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[259.97, 282.85, 443.65]</t>
+          <t>[1525.3, 392.03, 423.63]</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>29.51244801794846</v>
+        <v>71.77439404855872</v>
       </c>
       <c r="G176" t="n">
-        <v>28.75975483501632</v>
+        <v>50.72388957675417</v>
       </c>
       <c r="H176" t="n">
-        <v>9.441459560884647</v>
+        <v>5.237851243833036</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[6337.47, 5813.69, 5757.92]</t>
+          <t>[369.49, 423.32, 532.08]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[4865.05, 4811.11, 4921.76]</t>
+          <t>[392.03, 423.63, 527.44]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1136.124808053015</v>
+        <v>13.28882433088278</v>
       </c>
       <c r="G177" t="n">
-        <v>1103.71832169119</v>
+        <v>9.163607644187797</v>
       </c>
       <c r="H177" t="n">
-        <v>22.69768387365349</v>
+        <v>2.234243194759339</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[5406.53, 5360.11, 4843.03]</t>
+          <t>[426.52, 536.15, 900.63]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[4811.11, 4921.76, 4033.29]</t>
+          <t>[423.63, 527.44, 904.24]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>633.0764242333047</v>
+        <v>5.693978054789779</v>
       </c>
       <c r="G178" t="n">
-        <v>614.5036513996541</v>
+        <v>5.069776953325989</v>
       </c>
       <c r="H178" t="n">
-        <v>13.78624967852303</v>
+        <v>0.9108297328562099</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[4963.63, 4491.69, 4273.2]</t>
+          <t>[535.68, 899.86, 812.65]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[4921.76, 4033.29, 3836.02]</t>
+          <t>[527.44, 904.24, 819.04]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>366.5208308279969</v>
+        <v>6.530516221705475</v>
       </c>
       <c r="G179" t="n">
-        <v>312.4842125212746</v>
+        <v>6.337693838307132</v>
       </c>
       <c r="H179" t="n">
-        <v>7.870966436696357</v>
+        <v>0.9424181427040551</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[4469.79, 4251.85, 4478.81]</t>
+          <t>[898.13, 811.02, 1146.12]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[4033.29, 3836.02, 4988.31]</t>
+          <t>[904.24, 819.04, 1158.24]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>455.7185271905107</v>
+        <v>9.10184454454194</v>
       </c>
       <c r="G180" t="n">
-        <v>453.9436103216196</v>
+        <v>8.750030584556688</v>
       </c>
       <c r="H180" t="n">
-        <v>10.62548742194219</v>
+        <v>0.9004384296418095</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[4111.37, 4237.69, 3384.49]</t>
+          <t>[811.68, 1147.12, 550.83]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[3836.02, 4988.31, 2350.88]</t>
+          <t>[819.04, 1158.24, 573.3]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>754.4522611826386</v>
+        <v>15.08327247540004</v>
       </c>
       <c r="G181" t="n">
-        <v>686.5260690835083</v>
+        <v>13.647846614514</v>
       </c>
       <c r="H181" t="n">
-        <v>22.06414438702327</v>
+        <v>1.925691226949259</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[4123.05, 3623.37, 3899.19]</t>
+          <t>[1482.83, 692.69, 235.66]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[4988.31, 2350.88, 3378.76]</t>
+          <t>[1452.09, 692.96, 259.97]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>937.8598405638562</v>
+        <v>22.62675699860857</v>
       </c>
       <c r="G182" t="n">
-        <v>886.0582509077444</v>
+        <v>18.440680355071</v>
       </c>
       <c r="H182" t="n">
-        <v>28.95890816281381</v>
+        <v>3.836238819377622</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[3973.77, 4269.8, 5128.5]</t>
+          <t>[690.06, 234.65, 244.6]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[2350.88, 3378.76, 4625.15]</t>
+          <t>[692.96, 259.97, 282.85]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1107.712622320316</v>
+        <v>26.53782560060504</v>
       </c>
       <c r="G183" t="n">
-        <v>1005.76051792003</v>
+        <v>22.15599704006972</v>
       </c>
       <c r="H183" t="n">
-        <v>35.42932664355804</v>
+        <v>7.893828411026103</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[3811.44, 4730.34, 4991.98]</t>
+          <t>[234.85, 244.8, 420.54]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[3378.76, 4625.15, 4443.92]</t>
+          <t>[259.97, 282.85, 443.65]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>407.6967483355176</v>
+        <v>29.51244801794846</v>
       </c>
       <c r="G184" t="n">
-        <v>361.978353373386</v>
+        <v>28.75975483501632</v>
       </c>
       <c r="H184" t="n">
-        <v>9.137699910394517</v>
+        <v>9.441459560884647</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[4558.31, 4812.73, 4869.31]</t>
+          <t>[249.79, 428.99, 296.49]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[4625.15, 4443.92, 5402.06]</t>
+          <t>[282.85, 443.65, 328.67]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>376.0824050625843</v>
+        <v>27.94926572212285</v>
       </c>
       <c r="G185" t="n">
-        <v>322.8016231740603</v>
+        <v>26.63446933811078</v>
       </c>
       <c r="H185" t="n">
-        <v>6.535474116784767</v>
+        <v>8.261383580758315</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[437.84, 302.4, 50.0]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[443.65, 328.67, 73.46]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>20.60742880737102</v>
+      </c>
+      <c r="G186" t="n">
+        <v>18.51244134075087</v>
+      </c>
+      <c r="H186" t="n">
+        <v>13.74453251732374</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[303.01, 50.11, 197.18]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[328.67, 73.46, 226.5]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>26.22306544850049</v>
+      </c>
+      <c r="G187" t="n">
+        <v>26.10764357254185</v>
+      </c>
+      <c r="H187" t="n">
+        <v>17.51093833716762</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[50.72, 199.73, 304.39]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[73.46, 226.5, 324.2]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>23.28264843198132</v>
+      </c>
+      <c r="G188" t="n">
+        <v>23.1075948084638</v>
+      </c>
+      <c r="H188" t="n">
+        <v>16.29658211897443</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[207.41, 309.05, 439.46]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[226.5, 324.2, 431.65]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>14.7736854481468</v>
+      </c>
+      <c r="G189" t="n">
+        <v>14.01513804224761</v>
+      </c>
+      <c r="H189" t="n">
+        <v>4.969671759987201</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[316.04, 449.72, 517.48]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[324.2, 431.65, 492.27]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>18.52098439059548</v>
+      </c>
+      <c r="G190" t="n">
+        <v>17.15087041604869</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3.942521759092866</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[454.22, 522.06, 1057.79]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[431.65, 492.27, 989.64]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>44.87539204752238</v>
+      </c>
+      <c r="G191" t="n">
+        <v>40.17127757900494</v>
+      </c>
+      <c r="H191" t="n">
+        <v>6.055872258134841</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[3811.44, 4730.34, 4991.98]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[3378.76, 4625.15, 4443.92]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>407.6967483355176</v>
+      </c>
+      <c r="G192" t="n">
+        <v>361.978353373386</v>
+      </c>
+      <c r="H192" t="n">
+        <v>9.137699910394517</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[4558.31, 4812.73, 4869.31]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[4625.15, 4443.92, 5402.06]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>376.0824050625843</v>
+      </c>
+      <c r="G193" t="n">
+        <v>322.8016231740603</v>
+      </c>
+      <c r="H193" t="n">
+        <v>6.535474116784767</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[4834.6, 4892.55, 6620.68]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[4443.92, 5402.06, 8866.36]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>1348.495810025739</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>1048.626277759818</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>14.51712362080145</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[4765.53, 6448.06, 4033.13]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[5402.06, 8866.36, 4447.97]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>1463.491901818265</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1156.555848338432</v>
+      </c>
+      <c r="H195" t="n">
+        <v>16.12818744874809</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[6704.03, 4181.91, 4246.37]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[8866.36, 4447.97, 4266.88]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1257.894561780161</v>
+      </c>
+      <c r="G196" t="n">
+        <v>816.300395964714</v>
+      </c>
+      <c r="H196" t="n">
+        <v>10.28343003689212</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[4502.39, 4573.18, 4687.51]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[4447.97, 4266.88, 4540.22]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>198.7266533444671</v>
+      </c>
+      <c r="G197" t="n">
+        <v>169.338477301257</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3.882087411405963</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[4556.5, 4671.23, 3923.52]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[4266.88, 4540.22, 3939.72]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>183.7634061126324</v>
+      </c>
+      <c r="G198" t="n">
+        <v>145.6099528062211</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3.361450267619091</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[4590.2, 3854.92, 3758.32]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[4540.22, 3939.72, 3631.9]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>92.50377072803975</v>
+      </c>
+      <c r="G199" t="n">
+        <v>87.06522759709226</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2.24466573977941</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[3843.92, 3747.57, 4663.25]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[3939.72, 3631.9, 3915.0]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>440.6204047142259</v>
+      </c>
+      <c r="G200" t="n">
+        <v>319.9096981527617</v>
+      </c>
+      <c r="H200" t="n">
+        <v>8.243036396249103</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[3771.65, 4692.99, 2428.93]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[3631.9, 3915.0, 2576.47]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>464.242307609964</v>
+      </c>
+      <c r="G201" t="n">
+        <v>355.0908945791609</v>
+      </c>
+      <c r="H201" t="n">
+        <v>9.815368247385708</v>
       </c>
     </row>
   </sheetData>
